--- a/space-battleship/config_excel/hyperspace_enemies.xlsx
+++ b/space-battleship/config_excel/hyperspace_enemies.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="敌人" sheetId="1" r:id="R3e1c862466144f07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器安装" sheetId="2" r:id="R7b3dd631c4c34d00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="编队" sheetId="3" r:id="R57279a14edcf4012"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="编队槽位" sheetId="4" r:id="R0fbc1b14871e4240"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="路线编排" sheetId="5" r:id="R4723077b3e154810"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励参考" sheetId="6" r:id="R95368d053f764809"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成员分配" sheetId="7" r:id="R533f8b7108f2408c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="早段回退预算" sheetId="8" r:id="R757992454e7d4567"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="敌人" sheetId="1" r:id="R6789623c6d9b4363"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器安装" sheetId="2" r:id="Rd0f5fa439d81496a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="编队" sheetId="3" r:id="Re49698843dc3428b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="编队槽位" sheetId="4" r:id="Re7c068b31e104bf0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="路线编排" sheetId="5" r:id="R19390a07dc404aae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励参考" sheetId="6" r:id="R37548412ee21428e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成员分配" sheetId="7" r:id="R3e63c358bc494d43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="早段回退预算" sheetId="8" r:id="Rfe63e82ef4b841a2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -418,7 +418,7 @@
         <x:v>damage_multiplier</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="138" customHeight="1">
+    <x:row r="2" ht="152" customHeight="1">
       <x:c r="A2" s="10" t="str">
         <x:v>固定输出/随机选择顺序；物理行排序不改变它
 单位：0起序号
@@ -427,7 +427,7 @@
       <x:c r="B2" s="10" t="str">
         <x:v>现有独立异空间敌人ID
 单位：ID
-约束：正整数，当前223个既有ID；不得与主线ID冲突</x:v>
+约束：正整数，当前223个既有ID；不得与主线ID冲突；固定结构身份列，必须与基线等值，不能只改物理行冒充结构变化</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
         <x:v>已有敌人描述
@@ -435,42 +435,42 @@
 约束：必须基线等值；不创造美术/新指南</x:v>
       </x:c>
       <x:c r="D2" s="10" t="str">
-        <x:v>既有舰体尺寸档
+        <x:v>敌舰尺寸档位，影响战场几何/舰型；调大需重新检查阵型合法，不是生命倍率。
 单位：尺寸档
 约束：正整数且现有模型/几何支持</x:v>
       </x:c>
       <x:c r="E2" s="10" t="str">
-        <x:v>基础生命值
+        <x:v>敌人基础生命，另乘所选主线lifeRatio。调大更耐打，不复制主线等级倍率。
 单位：生命
 约束：&gt;0且有限</x:v>
       </x:c>
       <x:c r="F2" s="10" t="str">
-        <x:v>装甲抗性类别
+        <x:v>装甲伤害类型ID（0/1/2），与当前武器伤害类型匹配才使用相应抗性；不是减伤百分比。
 单位：枚举码
 约束：0/1/2</x:v>
       </x:c>
       <x:c r="G2" s="10" t="str">
-        <x:v>基础护盾容量
+        <x:v>敌人基础护盾容量，另乘所选生命倍率；0表示无盾。调大增加容量，不增生命本体。
 单位：护盾
 约束：≥0且有限</x:v>
       </x:c>
       <x:c r="H2" s="10" t="str">
-        <x:v>护盾抗性类别
+        <x:v>护盾伤害类型ID0/1/2，作用于盾的类型抗性，和装甲类型分别处理。
 单位：枚举码
 约束：0/1/2</x:v>
       </x:c>
       <x:c r="I2" s="10" t="str">
-        <x:v>每秒最大护盾恢复比例
+        <x:v>护盾恢复比例参数；按主线敌盾现有规则处理，调大恢复更快，0禁恢复；需结合盾容量。
 单位：比例/游戏秒
 约束：≥0且有限</x:v>
       </x:c>
       <x:c r="J2" s="10" t="str">
-        <x:v>实际命中后护盾恢复延迟
+        <x:v>护盾被命中后的恢复等待游戏秒；调大更晚恢复，0为立即恢复条件。
 单位：游戏秒
 约束：≥0且有限</x:v>
       </x:c>
       <x:c r="K2" s="10" t="str">
-        <x:v>基础武器伤害倍率
+        <x:v>敌人攻击基础乘数，另继承所选主线atkRatio；调大造成更多伤害，不改变攻击间隔。
 单位：无量纲
 约束：≥0且有限</x:v>
       </x:c>
@@ -8340,16 +8340,16 @@
         <x:v>weapon_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="138" customHeight="1">
+    <x:row r="2" ht="180" customHeight="1">
       <x:c r="A2" s="10" t="str">
         <x:v>异空间敌人外键
 单位：ID
-约束：必须存在于异空间敌人</x:v>
+约束：必须存在于异空间敌人；固定结构身份列，必须与基线等值，不能只改物理行冒充结构变化</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>固定输出/随机选择顺序；物理行排序不改变它
 单位：0起序号
-约束：按作用域唯一且连续；与冻结基线同ID同序号；锁定；导出必须按它排序</x:v>
+约束：按作用域唯一且连续；与冻结基线同ID同序号；锁定；导出必须按它排序；固定结构身份列，必须与基线等值，不能只改物理行冒充结构变化</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
         <x:v>现有敌武器安装键
@@ -10843,7 +10843,7 @@
         <x:v>reward_reference_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="138" customHeight="1">
+    <x:row r="2" ht="152" customHeight="1">
       <x:c r="A2" s="10" t="str">
         <x:v>固定输出/随机选择顺序；物理行排序不改变它
 单位：0起序号
@@ -10852,7 +10852,7 @@
       <x:c r="B2" s="10" t="str">
         <x:v>现有四十组独立编队ID
 单位：ID
-约束：正整数，当前7001..7040既有集合，不与主线冲突</x:v>
+约束：正整数，当前7001..7040既有集合，不与主线冲突；固定结构身份列，必须与基线等值，不能只改物理行冒充结构变化</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
         <x:v>已有编队名称/描述
@@ -11600,29 +11600,29 @@
         <x:v>y</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="96" customHeight="1">
+    <x:row r="2" ht="166" customHeight="1">
       <x:c r="A2" s="10" t="str">
         <x:v>编队外键
 单位：ID
-约束：必须存在于异空间编队</x:v>
+约束：必须存在于异空间编队；固定结构身份列，必须与基线等值，不能只改物理行冒充结构变化</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>源15槽的实际索引
+        <x:v>15槽中的0起索引，保留不规则空位；目前schema锁定，不能标可编辑。
 单位：0起索引
-约束：0..14，group内唯一，不能自动密排</x:v>
+约束：0..14，group内唯一，不能自动密排；固定结构身份列，必须与基线等值，不能只改物理行冒充结构变化</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
-        <x:v>该非空槽异空间敌人
+        <x:v>该现有非空槽使用的异空间敌ID，替换需保持合法尺寸/几何及recipe衍生ID一致。
 单位：ID
 约束：必须存在于异空间敌人</x:v>
       </x:c>
       <x:c r="D2" s="10" t="str">
-        <x:v>显式阵型横坐标
+        <x:v>逻辑战场横坐标，调大向右；范围54..518，非像素截图坐标。
 单位：逻辑战场单位
 约束：有限且54..518；实际几何合法</x:v>
       </x:c>
       <x:c r="E2" s="10" t="str">
-        <x:v>显式阵型纵坐标
+        <x:v>逻辑战场纵坐标，调大向下；范围80..350，检查前后/中心扇区。
 单位：逻辑战场单位
 约束：有限且80..350；大型舰前后顺序/中心扇区合法</x:v>
       </x:c>
@@ -11648,7 +11648,7 @@
       <x:c r="A4" s="17" t="n">
         <x:v>7001</x:v>
       </x:c>
-      <x:c r="B4" s="21" t="n">
+      <x:c r="B4" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="21" t="n">
@@ -11665,7 +11665,7 @@
       <x:c r="A5" s="17" t="n">
         <x:v>7001</x:v>
       </x:c>
-      <x:c r="B5" s="21" t="n">
+      <x:c r="B5" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="21" t="n">
@@ -11682,7 +11682,7 @@
       <x:c r="A6" s="17" t="n">
         <x:v>7002</x:v>
       </x:c>
-      <x:c r="B6" s="21" t="n">
+      <x:c r="B6" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="21" t="n">
@@ -11699,7 +11699,7 @@
       <x:c r="A7" s="17" t="n">
         <x:v>7002</x:v>
       </x:c>
-      <x:c r="B7" s="21" t="n">
+      <x:c r="B7" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C7" s="21" t="n">
@@ -11716,7 +11716,7 @@
       <x:c r="A8" s="17" t="n">
         <x:v>7002</x:v>
       </x:c>
-      <x:c r="B8" s="21" t="n">
+      <x:c r="B8" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C8" s="21" t="n">
@@ -11733,7 +11733,7 @@
       <x:c r="A9" s="17" t="n">
         <x:v>7003</x:v>
       </x:c>
-      <x:c r="B9" s="21" t="n">
+      <x:c r="B9" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C9" s="21" t="n">
@@ -11750,7 +11750,7 @@
       <x:c r="A10" s="17" t="n">
         <x:v>7003</x:v>
       </x:c>
-      <x:c r="B10" s="21" t="n">
+      <x:c r="B10" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="21" t="n">
@@ -11767,7 +11767,7 @@
       <x:c r="A11" s="17" t="n">
         <x:v>7003</x:v>
       </x:c>
-      <x:c r="B11" s="21" t="n">
+      <x:c r="B11" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C11" s="21" t="n">
@@ -11784,7 +11784,7 @@
       <x:c r="A12" s="17" t="n">
         <x:v>7003</x:v>
       </x:c>
-      <x:c r="B12" s="21" t="n">
+      <x:c r="B12" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C12" s="21" t="n">
@@ -11801,7 +11801,7 @@
       <x:c r="A13" s="17" t="n">
         <x:v>7004</x:v>
       </x:c>
-      <x:c r="B13" s="21" t="n">
+      <x:c r="B13" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C13" s="21" t="n">
@@ -11818,7 +11818,7 @@
       <x:c r="A14" s="17" t="n">
         <x:v>7004</x:v>
       </x:c>
-      <x:c r="B14" s="21" t="n">
+      <x:c r="B14" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C14" s="21" t="n">
@@ -11835,7 +11835,7 @@
       <x:c r="A15" s="17" t="n">
         <x:v>7004</x:v>
       </x:c>
-      <x:c r="B15" s="21" t="n">
+      <x:c r="B15" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C15" s="21" t="n">
@@ -11852,7 +11852,7 @@
       <x:c r="A16" s="17" t="n">
         <x:v>7004</x:v>
       </x:c>
-      <x:c r="B16" s="21" t="n">
+      <x:c r="B16" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C16" s="21" t="n">
@@ -11869,7 +11869,7 @@
       <x:c r="A17" s="17" t="n">
         <x:v>7004</x:v>
       </x:c>
-      <x:c r="B17" s="21" t="n">
+      <x:c r="B17" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C17" s="21" t="n">
@@ -11886,7 +11886,7 @@
       <x:c r="A18" s="17" t="n">
         <x:v>7005</x:v>
       </x:c>
-      <x:c r="B18" s="21" t="n">
+      <x:c r="B18" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C18" s="21" t="n">
@@ -11903,7 +11903,7 @@
       <x:c r="A19" s="17" t="n">
         <x:v>7005</x:v>
       </x:c>
-      <x:c r="B19" s="21" t="n">
+      <x:c r="B19" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C19" s="21" t="n">
@@ -11920,7 +11920,7 @@
       <x:c r="A20" s="17" t="n">
         <x:v>7005</x:v>
       </x:c>
-      <x:c r="B20" s="21" t="n">
+      <x:c r="B20" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C20" s="21" t="n">
@@ -11937,7 +11937,7 @@
       <x:c r="A21" s="17" t="n">
         <x:v>7005</x:v>
       </x:c>
-      <x:c r="B21" s="21" t="n">
+      <x:c r="B21" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C21" s="21" t="n">
@@ -11954,7 +11954,7 @@
       <x:c r="A22" s="17" t="n">
         <x:v>7005</x:v>
       </x:c>
-      <x:c r="B22" s="21" t="n">
+      <x:c r="B22" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C22" s="21" t="n">
@@ -11971,7 +11971,7 @@
       <x:c r="A23" s="17" t="n">
         <x:v>7005</x:v>
       </x:c>
-      <x:c r="B23" s="21" t="n">
+      <x:c r="B23" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C23" s="21" t="n">
@@ -11988,7 +11988,7 @@
       <x:c r="A24" s="17" t="n">
         <x:v>7005</x:v>
       </x:c>
-      <x:c r="B24" s="21" t="n">
+      <x:c r="B24" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C24" s="21" t="n">
@@ -12005,7 +12005,7 @@
       <x:c r="A25" s="17" t="n">
         <x:v>7006</x:v>
       </x:c>
-      <x:c r="B25" s="21" t="n">
+      <x:c r="B25" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C25" s="21" t="n">
@@ -12022,7 +12022,7 @@
       <x:c r="A26" s="17" t="n">
         <x:v>7006</x:v>
       </x:c>
-      <x:c r="B26" s="21" t="n">
+      <x:c r="B26" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C26" s="21" t="n">
@@ -12039,7 +12039,7 @@
       <x:c r="A27" s="17" t="n">
         <x:v>7007</x:v>
       </x:c>
-      <x:c r="B27" s="21" t="n">
+      <x:c r="B27" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C27" s="21" t="n">
@@ -12056,7 +12056,7 @@
       <x:c r="A28" s="17" t="n">
         <x:v>7007</x:v>
       </x:c>
-      <x:c r="B28" s="21" t="n">
+      <x:c r="B28" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C28" s="21" t="n">
@@ -12073,7 +12073,7 @@
       <x:c r="A29" s="17" t="n">
         <x:v>7007</x:v>
       </x:c>
-      <x:c r="B29" s="21" t="n">
+      <x:c r="B29" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C29" s="21" t="n">
@@ -12090,7 +12090,7 @@
       <x:c r="A30" s="17" t="n">
         <x:v>7007</x:v>
       </x:c>
-      <x:c r="B30" s="21" t="n">
+      <x:c r="B30" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C30" s="21" t="n">
@@ -12107,7 +12107,7 @@
       <x:c r="A31" s="17" t="n">
         <x:v>7007</x:v>
       </x:c>
-      <x:c r="B31" s="21" t="n">
+      <x:c r="B31" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C31" s="21" t="n">
@@ -12124,7 +12124,7 @@
       <x:c r="A32" s="17" t="n">
         <x:v>7007</x:v>
       </x:c>
-      <x:c r="B32" s="21" t="n">
+      <x:c r="B32" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C32" s="21" t="n">
@@ -12141,7 +12141,7 @@
       <x:c r="A33" s="17" t="n">
         <x:v>7007</x:v>
       </x:c>
-      <x:c r="B33" s="21" t="n">
+      <x:c r="B33" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C33" s="21" t="n">
@@ -12158,7 +12158,7 @@
       <x:c r="A34" s="17" t="n">
         <x:v>7008</x:v>
       </x:c>
-      <x:c r="B34" s="21" t="n">
+      <x:c r="B34" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C34" s="21" t="n">
@@ -12175,7 +12175,7 @@
       <x:c r="A35" s="17" t="n">
         <x:v>7008</x:v>
       </x:c>
-      <x:c r="B35" s="21" t="n">
+      <x:c r="B35" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C35" s="21" t="n">
@@ -12192,7 +12192,7 @@
       <x:c r="A36" s="17" t="n">
         <x:v>7008</x:v>
       </x:c>
-      <x:c r="B36" s="21" t="n">
+      <x:c r="B36" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C36" s="21" t="n">
@@ -12209,7 +12209,7 @@
       <x:c r="A37" s="17" t="n">
         <x:v>7009</x:v>
       </x:c>
-      <x:c r="B37" s="21" t="n">
+      <x:c r="B37" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C37" s="21" t="n">
@@ -12226,7 +12226,7 @@
       <x:c r="A38" s="17" t="n">
         <x:v>7009</x:v>
       </x:c>
-      <x:c r="B38" s="21" t="n">
+      <x:c r="B38" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C38" s="21" t="n">
@@ -12243,7 +12243,7 @@
       <x:c r="A39" s="17" t="n">
         <x:v>7009</x:v>
       </x:c>
-      <x:c r="B39" s="21" t="n">
+      <x:c r="B39" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C39" s="21" t="n">
@@ -12260,7 +12260,7 @@
       <x:c r="A40" s="17" t="n">
         <x:v>7009</x:v>
       </x:c>
-      <x:c r="B40" s="21" t="n">
+      <x:c r="B40" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C40" s="21" t="n">
@@ -12277,7 +12277,7 @@
       <x:c r="A41" s="17" t="n">
         <x:v>7010</x:v>
       </x:c>
-      <x:c r="B41" s="21" t="n">
+      <x:c r="B41" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C41" s="21" t="n">
@@ -12294,7 +12294,7 @@
       <x:c r="A42" s="17" t="n">
         <x:v>7010</x:v>
       </x:c>
-      <x:c r="B42" s="21" t="n">
+      <x:c r="B42" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C42" s="21" t="n">
@@ -12311,7 +12311,7 @@
       <x:c r="A43" s="17" t="n">
         <x:v>7010</x:v>
       </x:c>
-      <x:c r="B43" s="21" t="n">
+      <x:c r="B43" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C43" s="21" t="n">
@@ -12328,7 +12328,7 @@
       <x:c r="A44" s="17" t="n">
         <x:v>7010</x:v>
       </x:c>
-      <x:c r="B44" s="21" t="n">
+      <x:c r="B44" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C44" s="21" t="n">
@@ -12345,7 +12345,7 @@
       <x:c r="A45" s="17" t="n">
         <x:v>7010</x:v>
       </x:c>
-      <x:c r="B45" s="21" t="n">
+      <x:c r="B45" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C45" s="21" t="n">
@@ -12362,7 +12362,7 @@
       <x:c r="A46" s="17" t="n">
         <x:v>7010</x:v>
       </x:c>
-      <x:c r="B46" s="21" t="n">
+      <x:c r="B46" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C46" s="21" t="n">
@@ -12379,7 +12379,7 @@
       <x:c r="A47" s="17" t="n">
         <x:v>7011</x:v>
       </x:c>
-      <x:c r="B47" s="21" t="n">
+      <x:c r="B47" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C47" s="21" t="n">
@@ -12396,7 +12396,7 @@
       <x:c r="A48" s="17" t="n">
         <x:v>7011</x:v>
       </x:c>
-      <x:c r="B48" s="21" t="n">
+      <x:c r="B48" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C48" s="21" t="n">
@@ -12413,7 +12413,7 @@
       <x:c r="A49" s="17" t="n">
         <x:v>7011</x:v>
       </x:c>
-      <x:c r="B49" s="21" t="n">
+      <x:c r="B49" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C49" s="21" t="n">
@@ -12430,7 +12430,7 @@
       <x:c r="A50" s="17" t="n">
         <x:v>7011</x:v>
       </x:c>
-      <x:c r="B50" s="21" t="n">
+      <x:c r="B50" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C50" s="21" t="n">
@@ -12447,7 +12447,7 @@
       <x:c r="A51" s="17" t="n">
         <x:v>7012</x:v>
       </x:c>
-      <x:c r="B51" s="21" t="n">
+      <x:c r="B51" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C51" s="21" t="n">
@@ -12464,7 +12464,7 @@
       <x:c r="A52" s="17" t="n">
         <x:v>7012</x:v>
       </x:c>
-      <x:c r="B52" s="21" t="n">
+      <x:c r="B52" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C52" s="21" t="n">
@@ -12481,7 +12481,7 @@
       <x:c r="A53" s="17" t="n">
         <x:v>7012</x:v>
       </x:c>
-      <x:c r="B53" s="21" t="n">
+      <x:c r="B53" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C53" s="21" t="n">
@@ -12498,7 +12498,7 @@
       <x:c r="A54" s="17" t="n">
         <x:v>7012</x:v>
       </x:c>
-      <x:c r="B54" s="21" t="n">
+      <x:c r="B54" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C54" s="21" t="n">
@@ -12515,7 +12515,7 @@
       <x:c r="A55" s="17" t="n">
         <x:v>7012</x:v>
       </x:c>
-      <x:c r="B55" s="21" t="n">
+      <x:c r="B55" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C55" s="21" t="n">
@@ -12532,7 +12532,7 @@
       <x:c r="A56" s="17" t="n">
         <x:v>7012</x:v>
       </x:c>
-      <x:c r="B56" s="21" t="n">
+      <x:c r="B56" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C56" s="21" t="n">
@@ -12549,7 +12549,7 @@
       <x:c r="A57" s="17" t="n">
         <x:v>7012</x:v>
       </x:c>
-      <x:c r="B57" s="21" t="n">
+      <x:c r="B57" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C57" s="21" t="n">
@@ -12566,7 +12566,7 @@
       <x:c r="A58" s="17" t="n">
         <x:v>7013</x:v>
       </x:c>
-      <x:c r="B58" s="21" t="n">
+      <x:c r="B58" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C58" s="21" t="n">
@@ -12583,7 +12583,7 @@
       <x:c r="A59" s="17" t="n">
         <x:v>7013</x:v>
       </x:c>
-      <x:c r="B59" s="21" t="n">
+      <x:c r="B59" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C59" s="21" t="n">
@@ -12600,7 +12600,7 @@
       <x:c r="A60" s="17" t="n">
         <x:v>7013</x:v>
       </x:c>
-      <x:c r="B60" s="21" t="n">
+      <x:c r="B60" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C60" s="21" t="n">
@@ -12617,7 +12617,7 @@
       <x:c r="A61" s="17" t="n">
         <x:v>7014</x:v>
       </x:c>
-      <x:c r="B61" s="21" t="n">
+      <x:c r="B61" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C61" s="21" t="n">
@@ -12634,7 +12634,7 @@
       <x:c r="A62" s="17" t="n">
         <x:v>7014</x:v>
       </x:c>
-      <x:c r="B62" s="21" t="n">
+      <x:c r="B62" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C62" s="21" t="n">
@@ -12651,7 +12651,7 @@
       <x:c r="A63" s="17" t="n">
         <x:v>7014</x:v>
       </x:c>
-      <x:c r="B63" s="21" t="n">
+      <x:c r="B63" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C63" s="21" t="n">
@@ -12668,7 +12668,7 @@
       <x:c r="A64" s="17" t="n">
         <x:v>7014</x:v>
       </x:c>
-      <x:c r="B64" s="21" t="n">
+      <x:c r="B64" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C64" s="21" t="n">
@@ -12685,7 +12685,7 @@
       <x:c r="A65" s="17" t="n">
         <x:v>7014</x:v>
       </x:c>
-      <x:c r="B65" s="21" t="n">
+      <x:c r="B65" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C65" s="21" t="n">
@@ -12702,7 +12702,7 @@
       <x:c r="A66" s="17" t="n">
         <x:v>7015</x:v>
       </x:c>
-      <x:c r="B66" s="21" t="n">
+      <x:c r="B66" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C66" s="21" t="n">
@@ -12719,7 +12719,7 @@
       <x:c r="A67" s="17" t="n">
         <x:v>7015</x:v>
       </x:c>
-      <x:c r="B67" s="21" t="n">
+      <x:c r="B67" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C67" s="21" t="n">
@@ -12736,7 +12736,7 @@
       <x:c r="A68" s="17" t="n">
         <x:v>7015</x:v>
       </x:c>
-      <x:c r="B68" s="21" t="n">
+      <x:c r="B68" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C68" s="21" t="n">
@@ -12753,7 +12753,7 @@
       <x:c r="A69" s="17" t="n">
         <x:v>7015</x:v>
       </x:c>
-      <x:c r="B69" s="21" t="n">
+      <x:c r="B69" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C69" s="21" t="n">
@@ -12770,7 +12770,7 @@
       <x:c r="A70" s="17" t="n">
         <x:v>7016</x:v>
       </x:c>
-      <x:c r="B70" s="21" t="n">
+      <x:c r="B70" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C70" s="21" t="n">
@@ -12787,7 +12787,7 @@
       <x:c r="A71" s="17" t="n">
         <x:v>7016</x:v>
       </x:c>
-      <x:c r="B71" s="21" t="n">
+      <x:c r="B71" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C71" s="21" t="n">
@@ -12804,7 +12804,7 @@
       <x:c r="A72" s="17" t="n">
         <x:v>7016</x:v>
       </x:c>
-      <x:c r="B72" s="21" t="n">
+      <x:c r="B72" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C72" s="21" t="n">
@@ -12821,7 +12821,7 @@
       <x:c r="A73" s="17" t="n">
         <x:v>7016</x:v>
       </x:c>
-      <x:c r="B73" s="21" t="n">
+      <x:c r="B73" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C73" s="21" t="n">
@@ -12838,7 +12838,7 @@
       <x:c r="A74" s="17" t="n">
         <x:v>7016</x:v>
       </x:c>
-      <x:c r="B74" s="21" t="n">
+      <x:c r="B74" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C74" s="21" t="n">
@@ -12855,7 +12855,7 @@
       <x:c r="A75" s="17" t="n">
         <x:v>7016</x:v>
       </x:c>
-      <x:c r="B75" s="21" t="n">
+      <x:c r="B75" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C75" s="21" t="n">
@@ -12872,7 +12872,7 @@
       <x:c r="A76" s="17" t="n">
         <x:v>7016</x:v>
       </x:c>
-      <x:c r="B76" s="21" t="n">
+      <x:c r="B76" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C76" s="21" t="n">
@@ -12889,7 +12889,7 @@
       <x:c r="A77" s="17" t="n">
         <x:v>7016</x:v>
       </x:c>
-      <x:c r="B77" s="21" t="n">
+      <x:c r="B77" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C77" s="21" t="n">
@@ -12906,7 +12906,7 @@
       <x:c r="A78" s="17" t="n">
         <x:v>7017</x:v>
       </x:c>
-      <x:c r="B78" s="21" t="n">
+      <x:c r="B78" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C78" s="21" t="n">
@@ -12923,7 +12923,7 @@
       <x:c r="A79" s="17" t="n">
         <x:v>7017</x:v>
       </x:c>
-      <x:c r="B79" s="21" t="n">
+      <x:c r="B79" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C79" s="21" t="n">
@@ -12940,7 +12940,7 @@
       <x:c r="A80" s="17" t="n">
         <x:v>7017</x:v>
       </x:c>
-      <x:c r="B80" s="21" t="n">
+      <x:c r="B80" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C80" s="21" t="n">
@@ -12957,7 +12957,7 @@
       <x:c r="A81" s="17" t="n">
         <x:v>7018</x:v>
       </x:c>
-      <x:c r="B81" s="21" t="n">
+      <x:c r="B81" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C81" s="21" t="n">
@@ -12974,7 +12974,7 @@
       <x:c r="A82" s="17" t="n">
         <x:v>7018</x:v>
       </x:c>
-      <x:c r="B82" s="21" t="n">
+      <x:c r="B82" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C82" s="21" t="n">
@@ -12991,7 +12991,7 @@
       <x:c r="A83" s="17" t="n">
         <x:v>7018</x:v>
       </x:c>
-      <x:c r="B83" s="21" t="n">
+      <x:c r="B83" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C83" s="21" t="n">
@@ -13008,7 +13008,7 @@
       <x:c r="A84" s="17" t="n">
         <x:v>7018</x:v>
       </x:c>
-      <x:c r="B84" s="21" t="n">
+      <x:c r="B84" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C84" s="21" t="n">
@@ -13025,7 +13025,7 @@
       <x:c r="A85" s="17" t="n">
         <x:v>7018</x:v>
       </x:c>
-      <x:c r="B85" s="21" t="n">
+      <x:c r="B85" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C85" s="21" t="n">
@@ -13042,7 +13042,7 @@
       <x:c r="A86" s="17" t="n">
         <x:v>7018</x:v>
       </x:c>
-      <x:c r="B86" s="21" t="n">
+      <x:c r="B86" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C86" s="21" t="n">
@@ -13059,7 +13059,7 @@
       <x:c r="A87" s="17" t="n">
         <x:v>7018</x:v>
       </x:c>
-      <x:c r="B87" s="21" t="n">
+      <x:c r="B87" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C87" s="21" t="n">
@@ -13076,7 +13076,7 @@
       <x:c r="A88" s="17" t="n">
         <x:v>7018</x:v>
       </x:c>
-      <x:c r="B88" s="21" t="n">
+      <x:c r="B88" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C88" s="21" t="n">
@@ -13093,7 +13093,7 @@
       <x:c r="A89" s="17" t="n">
         <x:v>7019</x:v>
       </x:c>
-      <x:c r="B89" s="21" t="n">
+      <x:c r="B89" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C89" s="21" t="n">
@@ -13110,7 +13110,7 @@
       <x:c r="A90" s="17" t="n">
         <x:v>7019</x:v>
       </x:c>
-      <x:c r="B90" s="21" t="n">
+      <x:c r="B90" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C90" s="21" t="n">
@@ -13127,7 +13127,7 @@
       <x:c r="A91" s="17" t="n">
         <x:v>7019</x:v>
       </x:c>
-      <x:c r="B91" s="21" t="n">
+      <x:c r="B91" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C91" s="21" t="n">
@@ -13144,7 +13144,7 @@
       <x:c r="A92" s="17" t="n">
         <x:v>7019</x:v>
       </x:c>
-      <x:c r="B92" s="21" t="n">
+      <x:c r="B92" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C92" s="21" t="n">
@@ -13161,7 +13161,7 @@
       <x:c r="A93" s="17" t="n">
         <x:v>7019</x:v>
       </x:c>
-      <x:c r="B93" s="21" t="n">
+      <x:c r="B93" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C93" s="21" t="n">
@@ -13178,7 +13178,7 @@
       <x:c r="A94" s="17" t="n">
         <x:v>7019</x:v>
       </x:c>
-      <x:c r="B94" s="21" t="n">
+      <x:c r="B94" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C94" s="21" t="n">
@@ -13195,7 +13195,7 @@
       <x:c r="A95" s="17" t="n">
         <x:v>7020</x:v>
       </x:c>
-      <x:c r="B95" s="21" t="n">
+      <x:c r="B95" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C95" s="21" t="n">
@@ -13212,7 +13212,7 @@
       <x:c r="A96" s="17" t="n">
         <x:v>7020</x:v>
       </x:c>
-      <x:c r="B96" s="21" t="n">
+      <x:c r="B96" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C96" s="21" t="n">
@@ -13229,7 +13229,7 @@
       <x:c r="A97" s="17" t="n">
         <x:v>7020</x:v>
       </x:c>
-      <x:c r="B97" s="21" t="n">
+      <x:c r="B97" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C97" s="21" t="n">
@@ -13246,7 +13246,7 @@
       <x:c r="A98" s="17" t="n">
         <x:v>7020</x:v>
       </x:c>
-      <x:c r="B98" s="21" t="n">
+      <x:c r="B98" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C98" s="21" t="n">
@@ -13263,7 +13263,7 @@
       <x:c r="A99" s="17" t="n">
         <x:v>7020</x:v>
       </x:c>
-      <x:c r="B99" s="21" t="n">
+      <x:c r="B99" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C99" s="21" t="n">
@@ -13280,7 +13280,7 @@
       <x:c r="A100" s="17" t="n">
         <x:v>7021</x:v>
       </x:c>
-      <x:c r="B100" s="21" t="n">
+      <x:c r="B100" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C100" s="21" t="n">
@@ -13297,7 +13297,7 @@
       <x:c r="A101" s="17" t="n">
         <x:v>7021</x:v>
       </x:c>
-      <x:c r="B101" s="21" t="n">
+      <x:c r="B101" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C101" s="21" t="n">
@@ -13314,7 +13314,7 @@
       <x:c r="A102" s="17" t="n">
         <x:v>7021</x:v>
       </x:c>
-      <x:c r="B102" s="21" t="n">
+      <x:c r="B102" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C102" s="21" t="n">
@@ -13331,7 +13331,7 @@
       <x:c r="A103" s="17" t="n">
         <x:v>7021</x:v>
       </x:c>
-      <x:c r="B103" s="21" t="n">
+      <x:c r="B103" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C103" s="21" t="n">
@@ -13348,7 +13348,7 @@
       <x:c r="A104" s="17" t="n">
         <x:v>7021</x:v>
       </x:c>
-      <x:c r="B104" s="21" t="n">
+      <x:c r="B104" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C104" s="21" t="n">
@@ -13365,7 +13365,7 @@
       <x:c r="A105" s="17" t="n">
         <x:v>7021</x:v>
       </x:c>
-      <x:c r="B105" s="21" t="n">
+      <x:c r="B105" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C105" s="21" t="n">
@@ -13382,7 +13382,7 @@
       <x:c r="A106" s="17" t="n">
         <x:v>7021</x:v>
       </x:c>
-      <x:c r="B106" s="21" t="n">
+      <x:c r="B106" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C106" s="21" t="n">
@@ -13399,7 +13399,7 @@
       <x:c r="A107" s="17" t="n">
         <x:v>7022</x:v>
       </x:c>
-      <x:c r="B107" s="21" t="n">
+      <x:c r="B107" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C107" s="21" t="n">
@@ -13416,7 +13416,7 @@
       <x:c r="A108" s="17" t="n">
         <x:v>7022</x:v>
       </x:c>
-      <x:c r="B108" s="21" t="n">
+      <x:c r="B108" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C108" s="21" t="n">
@@ -13433,7 +13433,7 @@
       <x:c r="A109" s="17" t="n">
         <x:v>7022</x:v>
       </x:c>
-      <x:c r="B109" s="21" t="n">
+      <x:c r="B109" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C109" s="21" t="n">
@@ -13450,7 +13450,7 @@
       <x:c r="A110" s="17" t="n">
         <x:v>7023</x:v>
       </x:c>
-      <x:c r="B110" s="21" t="n">
+      <x:c r="B110" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C110" s="21" t="n">
@@ -13467,7 +13467,7 @@
       <x:c r="A111" s="17" t="n">
         <x:v>7023</x:v>
       </x:c>
-      <x:c r="B111" s="21" t="n">
+      <x:c r="B111" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C111" s="21" t="n">
@@ -13484,7 +13484,7 @@
       <x:c r="A112" s="17" t="n">
         <x:v>7023</x:v>
       </x:c>
-      <x:c r="B112" s="21" t="n">
+      <x:c r="B112" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C112" s="21" t="n">
@@ -13501,7 +13501,7 @@
       <x:c r="A113" s="17" t="n">
         <x:v>7023</x:v>
       </x:c>
-      <x:c r="B113" s="21" t="n">
+      <x:c r="B113" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C113" s="21" t="n">
@@ -13518,7 +13518,7 @@
       <x:c r="A114" s="17" t="n">
         <x:v>7023</x:v>
       </x:c>
-      <x:c r="B114" s="21" t="n">
+      <x:c r="B114" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C114" s="21" t="n">
@@ -13535,7 +13535,7 @@
       <x:c r="A115" s="17" t="n">
         <x:v>7023</x:v>
       </x:c>
-      <x:c r="B115" s="21" t="n">
+      <x:c r="B115" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C115" s="21" t="n">
@@ -13552,7 +13552,7 @@
       <x:c r="A116" s="17" t="n">
         <x:v>7024</x:v>
       </x:c>
-      <x:c r="B116" s="21" t="n">
+      <x:c r="B116" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C116" s="21" t="n">
@@ -13569,7 +13569,7 @@
       <x:c r="A117" s="17" t="n">
         <x:v>7024</x:v>
       </x:c>
-      <x:c r="B117" s="21" t="n">
+      <x:c r="B117" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C117" s="21" t="n">
@@ -13586,7 +13586,7 @@
       <x:c r="A118" s="17" t="n">
         <x:v>7024</x:v>
       </x:c>
-      <x:c r="B118" s="21" t="n">
+      <x:c r="B118" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C118" s="21" t="n">
@@ -13603,7 +13603,7 @@
       <x:c r="A119" s="17" t="n">
         <x:v>7024</x:v>
       </x:c>
-      <x:c r="B119" s="21" t="n">
+      <x:c r="B119" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C119" s="21" t="n">
@@ -13620,7 +13620,7 @@
       <x:c r="A120" s="17" t="n">
         <x:v>7024</x:v>
       </x:c>
-      <x:c r="B120" s="21" t="n">
+      <x:c r="B120" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C120" s="21" t="n">
@@ -13637,7 +13637,7 @@
       <x:c r="A121" s="17" t="n">
         <x:v>7024</x:v>
       </x:c>
-      <x:c r="B121" s="21" t="n">
+      <x:c r="B121" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C121" s="21" t="n">
@@ -13654,7 +13654,7 @@
       <x:c r="A122" s="17" t="n">
         <x:v>7024</x:v>
       </x:c>
-      <x:c r="B122" s="21" t="n">
+      <x:c r="B122" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C122" s="21" t="n">
@@ -13671,7 +13671,7 @@
       <x:c r="A123" s="17" t="n">
         <x:v>7024</x:v>
       </x:c>
-      <x:c r="B123" s="21" t="n">
+      <x:c r="B123" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C123" s="21" t="n">
@@ -13688,7 +13688,7 @@
       <x:c r="A124" s="17" t="n">
         <x:v>7025</x:v>
       </x:c>
-      <x:c r="B124" s="21" t="n">
+      <x:c r="B124" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C124" s="21" t="n">
@@ -13705,7 +13705,7 @@
       <x:c r="A125" s="17" t="n">
         <x:v>7025</x:v>
       </x:c>
-      <x:c r="B125" s="21" t="n">
+      <x:c r="B125" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C125" s="21" t="n">
@@ -13722,7 +13722,7 @@
       <x:c r="A126" s="17" t="n">
         <x:v>7025</x:v>
       </x:c>
-      <x:c r="B126" s="21" t="n">
+      <x:c r="B126" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C126" s="21" t="n">
@@ -13739,7 +13739,7 @@
       <x:c r="A127" s="17" t="n">
         <x:v>7025</x:v>
       </x:c>
-      <x:c r="B127" s="21" t="n">
+      <x:c r="B127" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C127" s="21" t="n">
@@ -13756,7 +13756,7 @@
       <x:c r="A128" s="17" t="n">
         <x:v>7026</x:v>
       </x:c>
-      <x:c r="B128" s="21" t="n">
+      <x:c r="B128" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C128" s="21" t="n">
@@ -13773,7 +13773,7 @@
       <x:c r="A129" s="17" t="n">
         <x:v>7026</x:v>
       </x:c>
-      <x:c r="B129" s="21" t="n">
+      <x:c r="B129" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C129" s="21" t="n">
@@ -13790,7 +13790,7 @@
       <x:c r="A130" s="17" t="n">
         <x:v>7026</x:v>
       </x:c>
-      <x:c r="B130" s="21" t="n">
+      <x:c r="B130" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C130" s="21" t="n">
@@ -13807,7 +13807,7 @@
       <x:c r="A131" s="17" t="n">
         <x:v>7026</x:v>
       </x:c>
-      <x:c r="B131" s="21" t="n">
+      <x:c r="B131" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C131" s="21" t="n">
@@ -13824,7 +13824,7 @@
       <x:c r="A132" s="17" t="n">
         <x:v>7026</x:v>
       </x:c>
-      <x:c r="B132" s="21" t="n">
+      <x:c r="B132" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C132" s="21" t="n">
@@ -13841,7 +13841,7 @@
       <x:c r="A133" s="17" t="n">
         <x:v>7027</x:v>
       </x:c>
-      <x:c r="B133" s="21" t="n">
+      <x:c r="B133" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C133" s="21" t="n">
@@ -13858,7 +13858,7 @@
       <x:c r="A134" s="17" t="n">
         <x:v>7027</x:v>
       </x:c>
-      <x:c r="B134" s="21" t="n">
+      <x:c r="B134" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C134" s="21" t="n">
@@ -13875,7 +13875,7 @@
       <x:c r="A135" s="17" t="n">
         <x:v>7027</x:v>
       </x:c>
-      <x:c r="B135" s="21" t="n">
+      <x:c r="B135" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C135" s="21" t="n">
@@ -13892,7 +13892,7 @@
       <x:c r="A136" s="17" t="n">
         <x:v>7027</x:v>
       </x:c>
-      <x:c r="B136" s="21" t="n">
+      <x:c r="B136" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C136" s="21" t="n">
@@ -13909,7 +13909,7 @@
       <x:c r="A137" s="17" t="n">
         <x:v>7027</x:v>
       </x:c>
-      <x:c r="B137" s="21" t="n">
+      <x:c r="B137" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C137" s="21" t="n">
@@ -13926,7 +13926,7 @@
       <x:c r="A138" s="17" t="n">
         <x:v>7027</x:v>
       </x:c>
-      <x:c r="B138" s="21" t="n">
+      <x:c r="B138" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C138" s="21" t="n">
@@ -13943,7 +13943,7 @@
       <x:c r="A139" s="17" t="n">
         <x:v>7027</x:v>
       </x:c>
-      <x:c r="B139" s="21" t="n">
+      <x:c r="B139" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C139" s="21" t="n">
@@ -13960,7 +13960,7 @@
       <x:c r="A140" s="17" t="n">
         <x:v>7028</x:v>
       </x:c>
-      <x:c r="B140" s="21" t="n">
+      <x:c r="B140" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C140" s="21" t="n">
@@ -13977,7 +13977,7 @@
       <x:c r="A141" s="17" t="n">
         <x:v>7028</x:v>
       </x:c>
-      <x:c r="B141" s="21" t="n">
+      <x:c r="B141" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C141" s="21" t="n">
@@ -13994,7 +13994,7 @@
       <x:c r="A142" s="17" t="n">
         <x:v>7028</x:v>
       </x:c>
-      <x:c r="B142" s="21" t="n">
+      <x:c r="B142" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C142" s="21" t="n">
@@ -14011,7 +14011,7 @@
       <x:c r="A143" s="17" t="n">
         <x:v>7028</x:v>
       </x:c>
-      <x:c r="B143" s="21" t="n">
+      <x:c r="B143" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C143" s="21" t="n">
@@ -14028,7 +14028,7 @@
       <x:c r="A144" s="17" t="n">
         <x:v>7029</x:v>
       </x:c>
-      <x:c r="B144" s="21" t="n">
+      <x:c r="B144" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C144" s="21" t="n">
@@ -14045,7 +14045,7 @@
       <x:c r="A145" s="17" t="n">
         <x:v>7029</x:v>
       </x:c>
-      <x:c r="B145" s="21" t="n">
+      <x:c r="B145" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C145" s="21" t="n">
@@ -14062,7 +14062,7 @@
       <x:c r="A146" s="17" t="n">
         <x:v>7029</x:v>
       </x:c>
-      <x:c r="B146" s="21" t="n">
+      <x:c r="B146" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C146" s="21" t="n">
@@ -14079,7 +14079,7 @@
       <x:c r="A147" s="17" t="n">
         <x:v>7029</x:v>
       </x:c>
-      <x:c r="B147" s="21" t="n">
+      <x:c r="B147" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C147" s="21" t="n">
@@ -14096,7 +14096,7 @@
       <x:c r="A148" s="17" t="n">
         <x:v>7029</x:v>
       </x:c>
-      <x:c r="B148" s="21" t="n">
+      <x:c r="B148" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C148" s="21" t="n">
@@ -14113,7 +14113,7 @@
       <x:c r="A149" s="17" t="n">
         <x:v>7029</x:v>
       </x:c>
-      <x:c r="B149" s="21" t="n">
+      <x:c r="B149" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C149" s="21" t="n">
@@ -14130,7 +14130,7 @@
       <x:c r="A150" s="17" t="n">
         <x:v>7030</x:v>
       </x:c>
-      <x:c r="B150" s="21" t="n">
+      <x:c r="B150" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C150" s="21" t="n">
@@ -14147,7 +14147,7 @@
       <x:c r="A151" s="17" t="n">
         <x:v>7030</x:v>
       </x:c>
-      <x:c r="B151" s="21" t="n">
+      <x:c r="B151" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C151" s="21" t="n">
@@ -14164,7 +14164,7 @@
       <x:c r="A152" s="17" t="n">
         <x:v>7030</x:v>
       </x:c>
-      <x:c r="B152" s="21" t="n">
+      <x:c r="B152" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C152" s="21" t="n">
@@ -14181,7 +14181,7 @@
       <x:c r="A153" s="17" t="n">
         <x:v>7030</x:v>
       </x:c>
-      <x:c r="B153" s="21" t="n">
+      <x:c r="B153" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C153" s="21" t="n">
@@ -14198,7 +14198,7 @@
       <x:c r="A154" s="17" t="n">
         <x:v>7030</x:v>
       </x:c>
-      <x:c r="B154" s="21" t="n">
+      <x:c r="B154" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C154" s="21" t="n">
@@ -14215,7 +14215,7 @@
       <x:c r="A155" s="17" t="n">
         <x:v>7030</x:v>
       </x:c>
-      <x:c r="B155" s="21" t="n">
+      <x:c r="B155" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C155" s="21" t="n">
@@ -14232,7 +14232,7 @@
       <x:c r="A156" s="17" t="n">
         <x:v>7030</x:v>
       </x:c>
-      <x:c r="B156" s="21" t="n">
+      <x:c r="B156" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C156" s="21" t="n">
@@ -14249,7 +14249,7 @@
       <x:c r="A157" s="17" t="n">
         <x:v>7030</x:v>
       </x:c>
-      <x:c r="B157" s="21" t="n">
+      <x:c r="B157" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C157" s="21" t="n">
@@ -14266,7 +14266,7 @@
       <x:c r="A158" s="17" t="n">
         <x:v>7031</x:v>
       </x:c>
-      <x:c r="B158" s="21" t="n">
+      <x:c r="B158" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C158" s="21" t="n">
@@ -14283,7 +14283,7 @@
       <x:c r="A159" s="17" t="n">
         <x:v>7031</x:v>
       </x:c>
-      <x:c r="B159" s="21" t="n">
+      <x:c r="B159" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C159" s="21" t="n">
@@ -14300,7 +14300,7 @@
       <x:c r="A160" s="17" t="n">
         <x:v>7031</x:v>
       </x:c>
-      <x:c r="B160" s="21" t="n">
+      <x:c r="B160" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C160" s="21" t="n">
@@ -14317,7 +14317,7 @@
       <x:c r="A161" s="17" t="n">
         <x:v>7031</x:v>
       </x:c>
-      <x:c r="B161" s="21" t="n">
+      <x:c r="B161" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C161" s="21" t="n">
@@ -14334,7 +14334,7 @@
       <x:c r="A162" s="17" t="n">
         <x:v>7031</x:v>
       </x:c>
-      <x:c r="B162" s="21" t="n">
+      <x:c r="B162" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C162" s="21" t="n">
@@ -14351,7 +14351,7 @@
       <x:c r="A163" s="17" t="n">
         <x:v>7032</x:v>
       </x:c>
-      <x:c r="B163" s="21" t="n">
+      <x:c r="B163" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C163" s="21" t="n">
@@ -14368,7 +14368,7 @@
       <x:c r="A164" s="17" t="n">
         <x:v>7032</x:v>
       </x:c>
-      <x:c r="B164" s="21" t="n">
+      <x:c r="B164" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C164" s="21" t="n">
@@ -14385,7 +14385,7 @@
       <x:c r="A165" s="17" t="n">
         <x:v>7032</x:v>
       </x:c>
-      <x:c r="B165" s="21" t="n">
+      <x:c r="B165" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C165" s="21" t="n">
@@ -14402,7 +14402,7 @@
       <x:c r="A166" s="17" t="n">
         <x:v>7032</x:v>
       </x:c>
-      <x:c r="B166" s="21" t="n">
+      <x:c r="B166" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C166" s="21" t="n">
@@ -14419,7 +14419,7 @@
       <x:c r="A167" s="17" t="n">
         <x:v>7032</x:v>
       </x:c>
-      <x:c r="B167" s="21" t="n">
+      <x:c r="B167" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C167" s="21" t="n">
@@ -14436,7 +14436,7 @@
       <x:c r="A168" s="17" t="n">
         <x:v>7032</x:v>
       </x:c>
-      <x:c r="B168" s="21" t="n">
+      <x:c r="B168" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C168" s="21" t="n">
@@ -14453,7 +14453,7 @@
       <x:c r="A169" s="17" t="n">
         <x:v>7033</x:v>
       </x:c>
-      <x:c r="B169" s="21" t="n">
+      <x:c r="B169" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C169" s="21" t="n">
@@ -14470,7 +14470,7 @@
       <x:c r="A170" s="17" t="n">
         <x:v>7033</x:v>
       </x:c>
-      <x:c r="B170" s="21" t="n">
+      <x:c r="B170" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C170" s="21" t="n">
@@ -14487,7 +14487,7 @@
       <x:c r="A171" s="17" t="n">
         <x:v>7033</x:v>
       </x:c>
-      <x:c r="B171" s="21" t="n">
+      <x:c r="B171" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C171" s="21" t="n">
@@ -14504,7 +14504,7 @@
       <x:c r="A172" s="17" t="n">
         <x:v>7033</x:v>
       </x:c>
-      <x:c r="B172" s="21" t="n">
+      <x:c r="B172" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C172" s="21" t="n">
@@ -14521,7 +14521,7 @@
       <x:c r="A173" s="17" t="n">
         <x:v>7033</x:v>
       </x:c>
-      <x:c r="B173" s="21" t="n">
+      <x:c r="B173" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C173" s="21" t="n">
@@ -14538,7 +14538,7 @@
       <x:c r="A174" s="17" t="n">
         <x:v>7033</x:v>
       </x:c>
-      <x:c r="B174" s="21" t="n">
+      <x:c r="B174" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C174" s="21" t="n">
@@ -14555,7 +14555,7 @@
       <x:c r="A175" s="17" t="n">
         <x:v>7034</x:v>
       </x:c>
-      <x:c r="B175" s="21" t="n">
+      <x:c r="B175" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C175" s="21" t="n">
@@ -14572,7 +14572,7 @@
       <x:c r="A176" s="17" t="n">
         <x:v>7034</x:v>
       </x:c>
-      <x:c r="B176" s="21" t="n">
+      <x:c r="B176" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C176" s="21" t="n">
@@ -14589,7 +14589,7 @@
       <x:c r="A177" s="17" t="n">
         <x:v>7034</x:v>
       </x:c>
-      <x:c r="B177" s="21" t="n">
+      <x:c r="B177" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C177" s="21" t="n">
@@ -14606,7 +14606,7 @@
       <x:c r="A178" s="17" t="n">
         <x:v>7034</x:v>
       </x:c>
-      <x:c r="B178" s="21" t="n">
+      <x:c r="B178" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C178" s="21" t="n">
@@ -14623,7 +14623,7 @@
       <x:c r="A179" s="17" t="n">
         <x:v>7035</x:v>
       </x:c>
-      <x:c r="B179" s="21" t="n">
+      <x:c r="B179" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C179" s="21" t="n">
@@ -14640,7 +14640,7 @@
       <x:c r="A180" s="17" t="n">
         <x:v>7035</x:v>
       </x:c>
-      <x:c r="B180" s="21" t="n">
+      <x:c r="B180" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C180" s="21" t="n">
@@ -14657,7 +14657,7 @@
       <x:c r="A181" s="17" t="n">
         <x:v>7035</x:v>
       </x:c>
-      <x:c r="B181" s="21" t="n">
+      <x:c r="B181" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C181" s="21" t="n">
@@ -14674,7 +14674,7 @@
       <x:c r="A182" s="17" t="n">
         <x:v>7035</x:v>
       </x:c>
-      <x:c r="B182" s="21" t="n">
+      <x:c r="B182" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C182" s="21" t="n">
@@ -14691,7 +14691,7 @@
       <x:c r="A183" s="17" t="n">
         <x:v>7035</x:v>
       </x:c>
-      <x:c r="B183" s="21" t="n">
+      <x:c r="B183" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C183" s="21" t="n">
@@ -14708,7 +14708,7 @@
       <x:c r="A184" s="17" t="n">
         <x:v>7035</x:v>
       </x:c>
-      <x:c r="B184" s="21" t="n">
+      <x:c r="B184" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C184" s="21" t="n">
@@ -14725,7 +14725,7 @@
       <x:c r="A185" s="17" t="n">
         <x:v>7035</x:v>
       </x:c>
-      <x:c r="B185" s="21" t="n">
+      <x:c r="B185" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C185" s="21" t="n">
@@ -14742,7 +14742,7 @@
       <x:c r="A186" s="17" t="n">
         <x:v>7036</x:v>
       </x:c>
-      <x:c r="B186" s="21" t="n">
+      <x:c r="B186" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C186" s="21" t="n">
@@ -14759,7 +14759,7 @@
       <x:c r="A187" s="17" t="n">
         <x:v>7036</x:v>
       </x:c>
-      <x:c r="B187" s="21" t="n">
+      <x:c r="B187" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C187" s="21" t="n">
@@ -14776,7 +14776,7 @@
       <x:c r="A188" s="17" t="n">
         <x:v>7036</x:v>
       </x:c>
-      <x:c r="B188" s="21" t="n">
+      <x:c r="B188" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C188" s="21" t="n">
@@ -14793,7 +14793,7 @@
       <x:c r="A189" s="17" t="n">
         <x:v>7036</x:v>
       </x:c>
-      <x:c r="B189" s="21" t="n">
+      <x:c r="B189" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C189" s="21" t="n">
@@ -14810,7 +14810,7 @@
       <x:c r="A190" s="17" t="n">
         <x:v>7036</x:v>
       </x:c>
-      <x:c r="B190" s="21" t="n">
+      <x:c r="B190" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C190" s="21" t="n">
@@ -14827,7 +14827,7 @@
       <x:c r="A191" s="17" t="n">
         <x:v>7036</x:v>
       </x:c>
-      <x:c r="B191" s="21" t="n">
+      <x:c r="B191" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C191" s="21" t="n">
@@ -14844,7 +14844,7 @@
       <x:c r="A192" s="17" t="n">
         <x:v>7036</x:v>
       </x:c>
-      <x:c r="B192" s="21" t="n">
+      <x:c r="B192" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C192" s="21" t="n">
@@ -14861,7 +14861,7 @@
       <x:c r="A193" s="17" t="n">
         <x:v>7036</x:v>
       </x:c>
-      <x:c r="B193" s="21" t="n">
+      <x:c r="B193" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C193" s="21" t="n">
@@ -14878,7 +14878,7 @@
       <x:c r="A194" s="17" t="n">
         <x:v>7036</x:v>
       </x:c>
-      <x:c r="B194" s="21" t="n">
+      <x:c r="B194" s="17" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C194" s="21" t="n">
@@ -14895,7 +14895,7 @@
       <x:c r="A195" s="17" t="n">
         <x:v>7036</x:v>
       </x:c>
-      <x:c r="B195" s="21" t="n">
+      <x:c r="B195" s="17" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C195" s="21" t="n">
@@ -14912,7 +14912,7 @@
       <x:c r="A196" s="17" t="n">
         <x:v>7037</x:v>
       </x:c>
-      <x:c r="B196" s="21" t="n">
+      <x:c r="B196" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C196" s="21" t="n">
@@ -14929,7 +14929,7 @@
       <x:c r="A197" s="17" t="n">
         <x:v>7037</x:v>
       </x:c>
-      <x:c r="B197" s="21" t="n">
+      <x:c r="B197" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C197" s="21" t="n">
@@ -14946,7 +14946,7 @@
       <x:c r="A198" s="17" t="n">
         <x:v>7037</x:v>
       </x:c>
-      <x:c r="B198" s="21" t="n">
+      <x:c r="B198" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C198" s="21" t="n">
@@ -14963,7 +14963,7 @@
       <x:c r="A199" s="17" t="n">
         <x:v>7037</x:v>
       </x:c>
-      <x:c r="B199" s="21" t="n">
+      <x:c r="B199" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C199" s="21" t="n">
@@ -14980,7 +14980,7 @@
       <x:c r="A200" s="17" t="n">
         <x:v>7037</x:v>
       </x:c>
-      <x:c r="B200" s="21" t="n">
+      <x:c r="B200" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C200" s="21" t="n">
@@ -14997,7 +14997,7 @@
       <x:c r="A201" s="17" t="n">
         <x:v>7037</x:v>
       </x:c>
-      <x:c r="B201" s="21" t="n">
+      <x:c r="B201" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C201" s="21" t="n">
@@ -15014,7 +15014,7 @@
       <x:c r="A202" s="17" t="n">
         <x:v>7037</x:v>
       </x:c>
-      <x:c r="B202" s="21" t="n">
+      <x:c r="B202" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C202" s="21" t="n">
@@ -15031,7 +15031,7 @@
       <x:c r="A203" s="17" t="n">
         <x:v>7037</x:v>
       </x:c>
-      <x:c r="B203" s="21" t="n">
+      <x:c r="B203" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C203" s="21" t="n">
@@ -15048,7 +15048,7 @@
       <x:c r="A204" s="17" t="n">
         <x:v>7038</x:v>
       </x:c>
-      <x:c r="B204" s="21" t="n">
+      <x:c r="B204" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C204" s="21" t="n">
@@ -15065,7 +15065,7 @@
       <x:c r="A205" s="17" t="n">
         <x:v>7038</x:v>
       </x:c>
-      <x:c r="B205" s="21" t="n">
+      <x:c r="B205" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C205" s="21" t="n">
@@ -15082,7 +15082,7 @@
       <x:c r="A206" s="17" t="n">
         <x:v>7038</x:v>
       </x:c>
-      <x:c r="B206" s="21" t="n">
+      <x:c r="B206" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C206" s="21" t="n">
@@ -15099,7 +15099,7 @@
       <x:c r="A207" s="17" t="n">
         <x:v>7038</x:v>
       </x:c>
-      <x:c r="B207" s="21" t="n">
+      <x:c r="B207" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C207" s="21" t="n">
@@ -15116,7 +15116,7 @@
       <x:c r="A208" s="17" t="n">
         <x:v>7038</x:v>
       </x:c>
-      <x:c r="B208" s="21" t="n">
+      <x:c r="B208" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C208" s="21" t="n">
@@ -15133,7 +15133,7 @@
       <x:c r="A209" s="17" t="n">
         <x:v>7038</x:v>
       </x:c>
-      <x:c r="B209" s="21" t="n">
+      <x:c r="B209" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C209" s="21" t="n">
@@ -15150,7 +15150,7 @@
       <x:c r="A210" s="17" t="n">
         <x:v>7038</x:v>
       </x:c>
-      <x:c r="B210" s="21" t="n">
+      <x:c r="B210" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C210" s="21" t="n">
@@ -15167,7 +15167,7 @@
       <x:c r="A211" s="17" t="n">
         <x:v>7038</x:v>
       </x:c>
-      <x:c r="B211" s="21" t="n">
+      <x:c r="B211" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C211" s="21" t="n">
@@ -15184,7 +15184,7 @@
       <x:c r="A212" s="17" t="n">
         <x:v>7038</x:v>
       </x:c>
-      <x:c r="B212" s="21" t="n">
+      <x:c r="B212" s="17" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C212" s="21" t="n">
@@ -15201,7 +15201,7 @@
       <x:c r="A213" s="17" t="n">
         <x:v>7038</x:v>
       </x:c>
-      <x:c r="B213" s="21" t="n">
+      <x:c r="B213" s="17" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C213" s="21" t="n">
@@ -15218,7 +15218,7 @@
       <x:c r="A214" s="17" t="n">
         <x:v>7038</x:v>
       </x:c>
-      <x:c r="B214" s="21" t="n">
+      <x:c r="B214" s="17" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C214" s="21" t="n">
@@ -15235,7 +15235,7 @@
       <x:c r="A215" s="17" t="n">
         <x:v>7039</x:v>
       </x:c>
-      <x:c r="B215" s="21" t="n">
+      <x:c r="B215" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C215" s="21" t="n">
@@ -15252,7 +15252,7 @@
       <x:c r="A216" s="17" t="n">
         <x:v>7039</x:v>
       </x:c>
-      <x:c r="B216" s="21" t="n">
+      <x:c r="B216" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C216" s="21" t="n">
@@ -15269,7 +15269,7 @@
       <x:c r="A217" s="17" t="n">
         <x:v>7039</x:v>
       </x:c>
-      <x:c r="B217" s="21" t="n">
+      <x:c r="B217" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C217" s="21" t="n">
@@ -15286,7 +15286,7 @@
       <x:c r="A218" s="17" t="n">
         <x:v>7039</x:v>
       </x:c>
-      <x:c r="B218" s="21" t="n">
+      <x:c r="B218" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C218" s="21" t="n">
@@ -15303,7 +15303,7 @@
       <x:c r="A219" s="17" t="n">
         <x:v>7039</x:v>
       </x:c>
-      <x:c r="B219" s="21" t="n">
+      <x:c r="B219" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C219" s="21" t="n">
@@ -15320,7 +15320,7 @@
       <x:c r="A220" s="17" t="n">
         <x:v>7040</x:v>
       </x:c>
-      <x:c r="B220" s="21" t="n">
+      <x:c r="B220" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C220" s="21" t="n">
@@ -15337,7 +15337,7 @@
       <x:c r="A221" s="17" t="n">
         <x:v>7040</x:v>
       </x:c>
-      <x:c r="B221" s="21" t="n">
+      <x:c r="B221" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C221" s="21" t="n">
@@ -15354,7 +15354,7 @@
       <x:c r="A222" s="17" t="n">
         <x:v>7040</x:v>
       </x:c>
-      <x:c r="B222" s="21" t="n">
+      <x:c r="B222" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C222" s="21" t="n">
@@ -15371,7 +15371,7 @@
       <x:c r="A223" s="17" t="n">
         <x:v>7040</x:v>
       </x:c>
-      <x:c r="B223" s="21" t="n">
+      <x:c r="B223" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C223" s="21" t="n">
@@ -15388,7 +15388,7 @@
       <x:c r="A224" s="17" t="n">
         <x:v>7040</x:v>
       </x:c>
-      <x:c r="B224" s="21" t="n">
+      <x:c r="B224" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C224" s="21" t="n">
@@ -15405,7 +15405,7 @@
       <x:c r="A225" s="17" t="n">
         <x:v>7040</x:v>
       </x:c>
-      <x:c r="B225" s="21" t="n">
+      <x:c r="B225" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C225" s="21" t="n">
@@ -15422,7 +15422,7 @@
       <x:c r="A226" s="17" t="n">
         <x:v>7040</x:v>
       </x:c>
-      <x:c r="B226" s="21" t="n">
+      <x:c r="B226" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C226" s="21" t="n">
@@ -15464,24 +15464,24 @@
         <x:v>group_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="138" customHeight="1">
+    <x:row r="2" ht="180" customHeight="1">
       <x:c r="A2" s="10" t="str">
         <x:v>异空间路线外键
 单位：已有ID引用
-约束：必须存在于路线；保持当前引用，变更需跨表校验</x:v>
+约束：必须存在于路线；保持当前引用，变更需跨表校验；固定结构身份列，必须与基线等值，不能只改物理行冒充结构变化</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>战斗档位
 单位：档位
-约束：normal/elite/boss/ultimate固定顺序</x:v>
+约束：normal/elite/boss/ultimate固定顺序；固定结构身份列，必须与基线等值，不能只改物理行冒充结构变化</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
         <x:v>固定输出/随机选择顺序；物理行排序不改变它
 单位：0起序号
-约束：按作用域唯一且连续；与冻结基线同ID同序号；锁定；导出必须按它排序</x:v>
+约束：按作用域唯一且连续；与冻结基线同ID同序号；锁定；导出必须按它排序；固定结构身份列，必须与基线等值，不能只改物理行冒充结构变化</x:v>
       </x:c>
       <x:c r="D2" s="10" t="str">
-        <x:v>该档位有序编队ID
+        <x:v>该路线该档有序编队引用；必须唯一覆盖40组、档位匹配4/4/1/1。更换需与其他行联动，不能复制组突破数量。
 单位：ID
 约束：存在于异空间编队且档位一致；每路线4/4/1/1，无跨路线重复</x:v>
       </x:c>
@@ -16101,7 +16101,7 @@
       <x:c r="A2" s="10" t="str">
         <x:v>现有奖励参考设计键
 单位：稳定ID
-约束：仅已有实现/已验ID；不自动新增功能；非空；主键作用域唯一；阶段1是固定只读来源关联；catalog预算由正式主线及早段回退预算唯一派生</x:v>
+约束：仅已有实现/已验ID；不自动新增功能；非空；主键作用域唯一；阶段1是固定只读来源关联；catalog预算由正式主线及早段回退预算唯一派生；固定结构身份列，必须与基线等值，不能只改物理行冒充结构变化</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>现有正式主线原设计组引用
@@ -16124,7 +16124,7 @@
 约束：存在于正式monGroup；真实blocks从mon的drops读取；阶段1是固定只读来源关联；catalog预算由正式主线及早段回退预算唯一派生</x:v>
       </x:c>
       <x:c r="F2" s="10" t="str">
-        <x:v>既有早1..5、晚≥6规则与不可重建项
+        <x:v>已有主线实例预算由主线表派生；25无早段实例95块来自回退页；sources为冻结结构映射。不能以编辑备注改变预算。
 单位：只读说明
 约束：锁定；不把catalog未消费分界字段当参数；阶段1是固定只读来源关联；catalog预算由正式主线及早段回退预算唯一派生</x:v>
       </x:c>
@@ -16982,29 +16982,29 @@
         <x:v>reference_member_ordinal</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="180" customHeight="1">
+    <x:row r="2" ht="278" customHeight="1">
       <x:c r="A2" s="10" t="str">
         <x:v>异空间奖励组外键
 单位：ID
-约束：存在于异空间编队</x:v>
+约束：存在于异空间编队；固定结构身份列，必须与基线等值，不能只改物理行冒充结构变化</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>组内原recipe成员记录顺序
+        <x:v>组内原成员记录顺序，锁定；保留零预算成员位置，避免随机调用/奖励映射漂移。
 单位：0起序号
 约束：同group/slot重复值一致；组内唯一成员顺序连续；锁定；导出按它排列成员</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
         <x:v>实际收取该预算块的异空间非空槽
 单位：0起索引
-约束：必须为该组非空槽</x:v>
+约束：必须为该组非空槽；固定结构身份列，必须与基线等值，不能只改物理行冒充结构变化</x:v>
       </x:c>
       <x:c r="D2" s="10" t="str">
-        <x:v>同成员内原ordinal数组顺序；零预算成员填空
+        <x:v>同成员预算数组原顺序，锁定。空只用于零预算；物理行排序不改变输出。
 单位：0起序号
-约束：同group/slot内唯一连续，锁定；数组按它输出，不按ordinal数值猜排序</x:v>
+约束：同group/slot内唯一连续，锁定；数组按它输出，不按ordinal数值猜排序；固定结构身份列，必须与基线等值，不能只改物理行冒充结构变化</x:v>
       </x:c>
       <x:c r="E2" s="10" t="str">
-        <x:v>被分配的原参考成员序号
+        <x:v>源预算成员0起序号，0是第一个真实预算块；空表示该成员零预算，必须保留行。更换须全组完整覆盖且不重复；不填金额。
 单位：0起索引
 约束：覆盖0..reference_count-1且无重复；每个非空槽有成员记录，允许零预算；零预算成员必须保留一行，order与ordinal都为空，导出[]和jewelDropRolls=0</x:v>
       </x:c>
@@ -17033,7 +17033,7 @@
       <x:c r="B4" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C4" s="21" t="n">
+      <x:c r="C4" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="25" t="n">
@@ -17050,7 +17050,7 @@
       <x:c r="B5" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C5" s="21" t="n">
+      <x:c r="C5" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="25" t="n">
@@ -17067,7 +17067,7 @@
       <x:c r="B6" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C6" s="21" t="n">
+      <x:c r="C6" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D6" s="25" t="n">
@@ -17084,7 +17084,7 @@
       <x:c r="B7" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C7" s="21" t="n">
+      <x:c r="C7" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="25" t="n">
@@ -17101,7 +17101,7 @@
       <x:c r="B8" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C8" s="21" t="n">
+      <x:c r="C8" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="25" t="n">
@@ -17118,7 +17118,7 @@
       <x:c r="B9" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C9" s="21" t="n">
+      <x:c r="C9" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D9" s="25" t="n">
@@ -17135,7 +17135,7 @@
       <x:c r="B10" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="n">
+      <x:c r="C10" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="25" t="n">
@@ -17152,7 +17152,7 @@
       <x:c r="B11" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="21" t="n">
+      <x:c r="C11" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D11" s="25" t="n">
@@ -17169,7 +17169,7 @@
       <x:c r="B12" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="n">
+      <x:c r="C12" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D12" s="25" t="n">
@@ -17186,7 +17186,7 @@
       <x:c r="B13" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C13" s="21" t="n">
+      <x:c r="C13" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D13" s="20"/>
@@ -17199,7 +17199,7 @@
       <x:c r="B14" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="n">
+      <x:c r="C14" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="25" t="n">
@@ -17216,7 +17216,7 @@
       <x:c r="B15" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C15" s="21" t="n">
+      <x:c r="C15" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="25" t="n">
@@ -17233,7 +17233,7 @@
       <x:c r="B16" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C16" s="21" t="n">
+      <x:c r="C16" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="25" t="n">
@@ -17250,7 +17250,7 @@
       <x:c r="B17" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C17" s="21" t="n">
+      <x:c r="C17" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="25" t="n">
@@ -17267,7 +17267,7 @@
       <x:c r="B18" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C18" s="21" t="n">
+      <x:c r="C18" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D18" s="25" t="n">
@@ -17284,7 +17284,7 @@
       <x:c r="B19" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C19" s="21" t="n">
+      <x:c r="C19" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D19" s="25" t="n">
@@ -17301,7 +17301,7 @@
       <x:c r="B20" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C20" s="21" t="n">
+      <x:c r="C20" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D20" s="25" t="n">
@@ -17318,7 +17318,7 @@
       <x:c r="B21" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C21" s="21" t="n">
+      <x:c r="C21" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D21" s="25" t="n">
@@ -17335,7 +17335,7 @@
       <x:c r="B22" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C22" s="21" t="n">
+      <x:c r="C22" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D22" s="25" t="n">
@@ -17352,7 +17352,7 @@
       <x:c r="B23" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C23" s="21" t="n">
+      <x:c r="C23" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="25" t="n">
@@ -17369,7 +17369,7 @@
       <x:c r="B24" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C24" s="21" t="n">
+      <x:c r="C24" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="25" t="n">
@@ -17386,7 +17386,7 @@
       <x:c r="B25" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C25" s="21" t="n">
+      <x:c r="C25" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="25" t="n">
@@ -17403,7 +17403,7 @@
       <x:c r="B26" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C26" s="21" t="n">
+      <x:c r="C26" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D26" s="25" t="n">
@@ -17420,7 +17420,7 @@
       <x:c r="B27" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C27" s="21" t="n">
+      <x:c r="C27" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D27" s="25" t="n">
@@ -17437,7 +17437,7 @@
       <x:c r="B28" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C28" s="21" t="n">
+      <x:c r="C28" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D28" s="25" t="n">
@@ -17454,7 +17454,7 @@
       <x:c r="B29" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C29" s="21" t="n">
+      <x:c r="C29" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D29" s="25" t="n">
@@ -17471,7 +17471,7 @@
       <x:c r="B30" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C30" s="21" t="n">
+      <x:c r="C30" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D30" s="25" t="n">
@@ -17488,7 +17488,7 @@
       <x:c r="B31" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C31" s="21" t="n">
+      <x:c r="C31" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D31" s="25" t="n">
@@ -17505,7 +17505,7 @@
       <x:c r="B32" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C32" s="21" t="n">
+      <x:c r="C32" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D32" s="25" t="n">
@@ -17522,7 +17522,7 @@
       <x:c r="B33" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C33" s="21" t="n">
+      <x:c r="C33" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D33" s="25" t="n">
@@ -17539,7 +17539,7 @@
       <x:c r="B34" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C34" s="21" t="n">
+      <x:c r="C34" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D34" s="25" t="n">
@@ -17556,7 +17556,7 @@
       <x:c r="B35" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C35" s="21" t="n">
+      <x:c r="C35" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D35" s="25" t="n">
@@ -17573,7 +17573,7 @@
       <x:c r="B36" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C36" s="21" t="n">
+      <x:c r="C36" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D36" s="25" t="n">
@@ -17590,7 +17590,7 @@
       <x:c r="B37" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C37" s="21" t="n">
+      <x:c r="C37" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D37" s="25" t="n">
@@ -17607,7 +17607,7 @@
       <x:c r="B38" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C38" s="21" t="n">
+      <x:c r="C38" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="25" t="n">
@@ -17624,7 +17624,7 @@
       <x:c r="B39" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C39" s="21" t="n">
+      <x:c r="C39" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="25" t="n">
@@ -17641,7 +17641,7 @@
       <x:c r="B40" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C40" s="21" t="n">
+      <x:c r="C40" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D40" s="25" t="n">
@@ -17658,7 +17658,7 @@
       <x:c r="B41" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C41" s="21" t="n">
+      <x:c r="C41" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D41" s="25" t="n">
@@ -17675,7 +17675,7 @@
       <x:c r="B42" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C42" s="21" t="n">
+      <x:c r="C42" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D42" s="25" t="n">
@@ -17692,7 +17692,7 @@
       <x:c r="B43" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C43" s="21" t="n">
+      <x:c r="C43" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D43" s="25" t="n">
@@ -17709,7 +17709,7 @@
       <x:c r="B44" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C44" s="21" t="n">
+      <x:c r="C44" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D44" s="25" t="n">
@@ -17726,7 +17726,7 @@
       <x:c r="B45" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C45" s="21" t="n">
+      <x:c r="C45" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D45" s="25" t="n">
@@ -17743,7 +17743,7 @@
       <x:c r="B46" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C46" s="21" t="n">
+      <x:c r="C46" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D46" s="25" t="n">
@@ -17760,7 +17760,7 @@
       <x:c r="B47" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C47" s="21" t="n">
+      <x:c r="C47" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D47" s="25" t="n">
@@ -17777,7 +17777,7 @@
       <x:c r="B48" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C48" s="21" t="n">
+      <x:c r="C48" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D48" s="25" t="n">
@@ -17794,7 +17794,7 @@
       <x:c r="B49" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C49" s="21" t="n">
+      <x:c r="C49" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D49" s="25" t="n">
@@ -17811,7 +17811,7 @@
       <x:c r="B50" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C50" s="21" t="n">
+      <x:c r="C50" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D50" s="25" t="n">
@@ -17828,7 +17828,7 @@
       <x:c r="B51" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C51" s="21" t="n">
+      <x:c r="C51" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D51" s="25" t="n">
@@ -17845,7 +17845,7 @@
       <x:c r="B52" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C52" s="21" t="n">
+      <x:c r="C52" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D52" s="25" t="n">
@@ -17862,7 +17862,7 @@
       <x:c r="B53" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C53" s="21" t="n">
+      <x:c r="C53" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D53" s="25" t="n">
@@ -17879,7 +17879,7 @@
       <x:c r="B54" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C54" s="21" t="n">
+      <x:c r="C54" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D54" s="25" t="n">
@@ -17896,7 +17896,7 @@
       <x:c r="B55" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C55" s="21" t="n">
+      <x:c r="C55" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D55" s="25" t="n">
@@ -17913,7 +17913,7 @@
       <x:c r="B56" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C56" s="21" t="n">
+      <x:c r="C56" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D56" s="20"/>
@@ -17926,7 +17926,7 @@
       <x:c r="B57" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C57" s="21" t="n">
+      <x:c r="C57" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D57" s="25" t="n">
@@ -17943,7 +17943,7 @@
       <x:c r="B58" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C58" s="21" t="n">
+      <x:c r="C58" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D58" s="20"/>
@@ -17956,7 +17956,7 @@
       <x:c r="B59" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C59" s="21" t="n">
+      <x:c r="C59" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D59" s="20"/>
@@ -17969,7 +17969,7 @@
       <x:c r="B60" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C60" s="21" t="n">
+      <x:c r="C60" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D60" s="20"/>
@@ -17982,7 +17982,7 @@
       <x:c r="B61" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C61" s="21" t="n">
+      <x:c r="C61" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D61" s="20"/>
@@ -17995,7 +17995,7 @@
       <x:c r="B62" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C62" s="21" t="n">
+      <x:c r="C62" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D62" s="20"/>
@@ -18008,7 +18008,7 @@
       <x:c r="B63" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C63" s="21" t="n">
+      <x:c r="C63" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D63" s="25" t="n">
@@ -18025,7 +18025,7 @@
       <x:c r="B64" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C64" s="21" t="n">
+      <x:c r="C64" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D64" s="25" t="n">
@@ -18042,7 +18042,7 @@
       <x:c r="B65" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C65" s="21" t="n">
+      <x:c r="C65" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D65" s="25" t="n">
@@ -18059,7 +18059,7 @@
       <x:c r="B66" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C66" s="21" t="n">
+      <x:c r="C66" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D66" s="20"/>
@@ -18072,7 +18072,7 @@
       <x:c r="B67" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C67" s="21" t="n">
+      <x:c r="C67" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D67" s="25" t="n">
@@ -18089,7 +18089,7 @@
       <x:c r="B68" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C68" s="21" t="n">
+      <x:c r="C68" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D68" s="25" t="n">
@@ -18106,7 +18106,7 @@
       <x:c r="B69" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C69" s="21" t="n">
+      <x:c r="C69" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D69" s="25" t="n">
@@ -18123,7 +18123,7 @@
       <x:c r="B70" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C70" s="21" t="n">
+      <x:c r="C70" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D70" s="20"/>
@@ -18136,7 +18136,7 @@
       <x:c r="B71" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C71" s="21" t="n">
+      <x:c r="C71" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D71" s="20"/>
@@ -18149,7 +18149,7 @@
       <x:c r="B72" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C72" s="21" t="n">
+      <x:c r="C72" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D72" s="20"/>
@@ -18162,7 +18162,7 @@
       <x:c r="B73" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C73" s="21" t="n">
+      <x:c r="C73" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D73" s="20"/>
@@ -18175,7 +18175,7 @@
       <x:c r="B74" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C74" s="21" t="n">
+      <x:c r="C74" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D74" s="25" t="n">
@@ -18192,7 +18192,7 @@
       <x:c r="B75" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C75" s="21" t="n">
+      <x:c r="C75" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D75" s="25" t="n">
@@ -18209,7 +18209,7 @@
       <x:c r="B76" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C76" s="21" t="n">
+      <x:c r="C76" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D76" s="25" t="n">
@@ -18226,7 +18226,7 @@
       <x:c r="B77" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C77" s="21" t="n">
+      <x:c r="C77" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D77" s="25" t="n">
@@ -18243,7 +18243,7 @@
       <x:c r="B78" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C78" s="21" t="n">
+      <x:c r="C78" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D78" s="25" t="n">
@@ -18260,7 +18260,7 @@
       <x:c r="B79" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C79" s="21" t="n">
+      <x:c r="C79" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D79" s="25" t="n">
@@ -18277,7 +18277,7 @@
       <x:c r="B80" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C80" s="21" t="n">
+      <x:c r="C80" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D80" s="20"/>
@@ -18290,7 +18290,7 @@
       <x:c r="B81" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C81" s="21" t="n">
+      <x:c r="C81" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D81" s="20"/>
@@ -18303,7 +18303,7 @@
       <x:c r="B82" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C82" s="21" t="n">
+      <x:c r="C82" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D82" s="25" t="n">
@@ -18320,7 +18320,7 @@
       <x:c r="B83" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C83" s="21" t="n">
+      <x:c r="C83" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D83" s="20"/>
@@ -18333,7 +18333,7 @@
       <x:c r="B84" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C84" s="21" t="n">
+      <x:c r="C84" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D84" s="20"/>
@@ -18346,7 +18346,7 @@
       <x:c r="B85" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C85" s="21" t="n">
+      <x:c r="C85" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D85" s="20"/>
@@ -18359,7 +18359,7 @@
       <x:c r="B86" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C86" s="21" t="n">
+      <x:c r="C86" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D86" s="25" t="n">
@@ -18376,7 +18376,7 @@
       <x:c r="B87" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C87" s="21" t="n">
+      <x:c r="C87" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D87" s="25" t="n">
@@ -18393,7 +18393,7 @@
       <x:c r="B88" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C88" s="21" t="n">
+      <x:c r="C88" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D88" s="25" t="n">
@@ -18410,7 +18410,7 @@
       <x:c r="B89" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C89" s="21" t="n">
+      <x:c r="C89" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D89" s="25" t="n">
@@ -18427,7 +18427,7 @@
       <x:c r="B90" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C90" s="21" t="n">
+      <x:c r="C90" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D90" s="25" t="n">
@@ -18444,7 +18444,7 @@
       <x:c r="B91" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C91" s="21" t="n">
+      <x:c r="C91" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D91" s="25" t="n">
@@ -18461,7 +18461,7 @@
       <x:c r="B92" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C92" s="21" t="n">
+      <x:c r="C92" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D92" s="25" t="n">
@@ -18478,7 +18478,7 @@
       <x:c r="B93" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C93" s="21" t="n">
+      <x:c r="C93" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D93" s="25" t="n">
@@ -18495,7 +18495,7 @@
       <x:c r="B94" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C94" s="21" t="n">
+      <x:c r="C94" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D94" s="25" t="n">
@@ -18512,7 +18512,7 @@
       <x:c r="B95" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C95" s="21" t="n">
+      <x:c r="C95" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D95" s="25" t="n">
@@ -18529,7 +18529,7 @@
       <x:c r="B96" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C96" s="21" t="n">
+      <x:c r="C96" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D96" s="25" t="n">
@@ -18546,7 +18546,7 @@
       <x:c r="B97" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C97" s="21" t="n">
+      <x:c r="C97" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D97" s="25" t="n">
@@ -18563,7 +18563,7 @@
       <x:c r="B98" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C98" s="21" t="n">
+      <x:c r="C98" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D98" s="25" t="n">
@@ -18580,7 +18580,7 @@
       <x:c r="B99" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C99" s="21" t="n">
+      <x:c r="C99" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D99" s="25" t="n">
@@ -18597,7 +18597,7 @@
       <x:c r="B100" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C100" s="21" t="n">
+      <x:c r="C100" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D100" s="25" t="n">
@@ -18614,7 +18614,7 @@
       <x:c r="B101" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C101" s="21" t="n">
+      <x:c r="C101" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D101" s="25" t="n">
@@ -18631,7 +18631,7 @@
       <x:c r="B102" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C102" s="21" t="n">
+      <x:c r="C102" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D102" s="25" t="n">
@@ -18648,7 +18648,7 @@
       <x:c r="B103" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C103" s="21" t="n">
+      <x:c r="C103" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D103" s="25" t="n">
@@ -18665,7 +18665,7 @@
       <x:c r="B104" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C104" s="21" t="n">
+      <x:c r="C104" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D104" s="25" t="n">
@@ -18682,7 +18682,7 @@
       <x:c r="B105" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C105" s="21" t="n">
+      <x:c r="C105" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D105" s="25" t="n">
@@ -18699,7 +18699,7 @@
       <x:c r="B106" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C106" s="21" t="n">
+      <x:c r="C106" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D106" s="25" t="n">
@@ -18716,7 +18716,7 @@
       <x:c r="B107" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C107" s="21" t="n">
+      <x:c r="C107" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D107" s="25" t="n">
@@ -18733,7 +18733,7 @@
       <x:c r="B108" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C108" s="21" t="n">
+      <x:c r="C108" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D108" s="25" t="n">
@@ -18750,7 +18750,7 @@
       <x:c r="B109" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C109" s="21" t="n">
+      <x:c r="C109" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D109" s="25" t="n">
@@ -18767,7 +18767,7 @@
       <x:c r="B110" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C110" s="21" t="n">
+      <x:c r="C110" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D110" s="25" t="n">
@@ -18784,7 +18784,7 @@
       <x:c r="B111" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C111" s="21" t="n">
+      <x:c r="C111" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D111" s="20"/>
@@ -18797,7 +18797,7 @@
       <x:c r="B112" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C112" s="21" t="n">
+      <x:c r="C112" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D112" s="20"/>
@@ -18810,7 +18810,7 @@
       <x:c r="B113" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C113" s="21" t="n">
+      <x:c r="C113" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D113" s="20"/>
@@ -18823,7 +18823,7 @@
       <x:c r="B114" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C114" s="21" t="n">
+      <x:c r="C114" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D114" s="20"/>
@@ -18836,7 +18836,7 @@
       <x:c r="B115" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C115" s="21" t="n">
+      <x:c r="C115" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D115" s="25" t="n">
@@ -18853,7 +18853,7 @@
       <x:c r="B116" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C116" s="21" t="n">
+      <x:c r="C116" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D116" s="25" t="n">
@@ -18870,7 +18870,7 @@
       <x:c r="B117" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C117" s="21" t="n">
+      <x:c r="C117" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D117" s="25" t="n">
@@ -18887,7 +18887,7 @@
       <x:c r="B118" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C118" s="21" t="n">
+      <x:c r="C118" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D118" s="25" t="n">
@@ -18904,7 +18904,7 @@
       <x:c r="B119" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C119" s="21" t="n">
+      <x:c r="C119" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D119" s="25" t="n">
@@ -18921,7 +18921,7 @@
       <x:c r="B120" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C120" s="21" t="n">
+      <x:c r="C120" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D120" s="25" t="n">
@@ -18938,7 +18938,7 @@
       <x:c r="B121" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C121" s="21" t="n">
+      <x:c r="C121" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D121" s="25" t="n">
@@ -18955,7 +18955,7 @@
       <x:c r="B122" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C122" s="21" t="n">
+      <x:c r="C122" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D122" s="25" t="n">
@@ -18972,7 +18972,7 @@
       <x:c r="B123" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C123" s="21" t="n">
+      <x:c r="C123" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D123" s="25" t="n">
@@ -18989,7 +18989,7 @@
       <x:c r="B124" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C124" s="21" t="n">
+      <x:c r="C124" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D124" s="25" t="n">
@@ -19006,7 +19006,7 @@
       <x:c r="B125" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C125" s="21" t="n">
+      <x:c r="C125" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D125" s="25" t="n">
@@ -19023,7 +19023,7 @@
       <x:c r="B126" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C126" s="21" t="n">
+      <x:c r="C126" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D126" s="25" t="n">
@@ -19040,7 +19040,7 @@
       <x:c r="B127" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C127" s="21" t="n">
+      <x:c r="C127" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D127" s="25" t="n">
@@ -19057,7 +19057,7 @@
       <x:c r="B128" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C128" s="21" t="n">
+      <x:c r="C128" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D128" s="25" t="n">
@@ -19074,7 +19074,7 @@
       <x:c r="B129" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C129" s="21" t="n">
+      <x:c r="C129" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D129" s="25" t="n">
@@ -19091,7 +19091,7 @@
       <x:c r="B130" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C130" s="21" t="n">
+      <x:c r="C130" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D130" s="25" t="n">
@@ -19108,7 +19108,7 @@
       <x:c r="B131" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C131" s="21" t="n">
+      <x:c r="C131" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D131" s="25" t="n">
@@ -19125,7 +19125,7 @@
       <x:c r="B132" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C132" s="21" t="n">
+      <x:c r="C132" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D132" s="25" t="n">
@@ -19142,7 +19142,7 @@
       <x:c r="B133" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C133" s="21" t="n">
+      <x:c r="C133" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D133" s="25" t="n">
@@ -19159,7 +19159,7 @@
       <x:c r="B134" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C134" s="21" t="n">
+      <x:c r="C134" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D134" s="25" t="n">
@@ -19176,7 +19176,7 @@
       <x:c r="B135" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C135" s="21" t="n">
+      <x:c r="C135" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D135" s="20"/>
@@ -19189,7 +19189,7 @@
       <x:c r="B136" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C136" s="21" t="n">
+      <x:c r="C136" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D136" s="25" t="n">
@@ -19206,7 +19206,7 @@
       <x:c r="B137" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C137" s="21" t="n">
+      <x:c r="C137" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D137" s="25" t="n">
@@ -19223,7 +19223,7 @@
       <x:c r="B138" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C138" s="21" t="n">
+      <x:c r="C138" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D138" s="25" t="n">
@@ -19240,7 +19240,7 @@
       <x:c r="B139" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C139" s="21" t="n">
+      <x:c r="C139" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D139" s="25" t="n">
@@ -19257,7 +19257,7 @@
       <x:c r="B140" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C140" s="21" t="n">
+      <x:c r="C140" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D140" s="25" t="n">
@@ -19274,7 +19274,7 @@
       <x:c r="B141" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C141" s="21" t="n">
+      <x:c r="C141" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D141" s="20"/>
@@ -19287,7 +19287,7 @@
       <x:c r="B142" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C142" s="21" t="n">
+      <x:c r="C142" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D142" s="20"/>
@@ -19300,7 +19300,7 @@
       <x:c r="B143" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C143" s="21" t="n">
+      <x:c r="C143" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D143" s="25" t="n">
@@ -19317,7 +19317,7 @@
       <x:c r="B144" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C144" s="21" t="n">
+      <x:c r="C144" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D144" s="25" t="n">
@@ -19334,7 +19334,7 @@
       <x:c r="B145" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C145" s="21" t="n">
+      <x:c r="C145" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D145" s="25" t="n">
@@ -19351,7 +19351,7 @@
       <x:c r="B146" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C146" s="21" t="n">
+      <x:c r="C146" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D146" s="25" t="n">
@@ -19368,7 +19368,7 @@
       <x:c r="B147" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C147" s="21" t="n">
+      <x:c r="C147" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D147" s="25" t="n">
@@ -19385,7 +19385,7 @@
       <x:c r="B148" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C148" s="21" t="n">
+      <x:c r="C148" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D148" s="25" t="n">
@@ -19402,7 +19402,7 @@
       <x:c r="B149" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C149" s="21" t="n">
+      <x:c r="C149" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D149" s="25" t="n">
@@ -19419,7 +19419,7 @@
       <x:c r="B150" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C150" s="21" t="n">
+      <x:c r="C150" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D150" s="25" t="n">
@@ -19436,7 +19436,7 @@
       <x:c r="B151" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C151" s="21" t="n">
+      <x:c r="C151" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D151" s="20"/>
@@ -19449,7 +19449,7 @@
       <x:c r="B152" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C152" s="21" t="n">
+      <x:c r="C152" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D152" s="20"/>
@@ -19462,7 +19462,7 @@
       <x:c r="B153" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C153" s="21" t="n">
+      <x:c r="C153" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D153" s="25" t="n">
@@ -19479,7 +19479,7 @@
       <x:c r="B154" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C154" s="21" t="n">
+      <x:c r="C154" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D154" s="25" t="n">
@@ -19496,7 +19496,7 @@
       <x:c r="B155" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C155" s="21" t="n">
+      <x:c r="C155" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D155" s="25" t="n">
@@ -19513,7 +19513,7 @@
       <x:c r="B156" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C156" s="21" t="n">
+      <x:c r="C156" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D156" s="25" t="n">
@@ -19530,7 +19530,7 @@
       <x:c r="B157" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C157" s="21" t="n">
+      <x:c r="C157" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D157" s="25" t="n">
@@ -19547,7 +19547,7 @@
       <x:c r="B158" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C158" s="21" t="n">
+      <x:c r="C158" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D158" s="25" t="n">
@@ -19564,7 +19564,7 @@
       <x:c r="B159" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C159" s="21" t="n">
+      <x:c r="C159" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D159" s="25" t="n">
@@ -19581,7 +19581,7 @@
       <x:c r="B160" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C160" s="21" t="n">
+      <x:c r="C160" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D160" s="25" t="n">
@@ -19598,7 +19598,7 @@
       <x:c r="B161" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C161" s="21" t="n">
+      <x:c r="C161" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D161" s="25" t="n">
@@ -19615,7 +19615,7 @@
       <x:c r="B162" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C162" s="21" t="n">
+      <x:c r="C162" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D162" s="25" t="n">
@@ -19632,7 +19632,7 @@
       <x:c r="B163" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C163" s="21" t="n">
+      <x:c r="C163" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D163" s="25" t="n">
@@ -19649,7 +19649,7 @@
       <x:c r="B164" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C164" s="21" t="n">
+      <x:c r="C164" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D164" s="25" t="n">
@@ -19666,7 +19666,7 @@
       <x:c r="B165" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C165" s="21" t="n">
+      <x:c r="C165" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D165" s="25" t="n">
@@ -19683,7 +19683,7 @@
       <x:c r="B166" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C166" s="21" t="n">
+      <x:c r="C166" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D166" s="25" t="n">
@@ -19700,7 +19700,7 @@
       <x:c r="B167" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C167" s="21" t="n">
+      <x:c r="C167" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D167" s="25" t="n">
@@ -19717,7 +19717,7 @@
       <x:c r="B168" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C168" s="21" t="n">
+      <x:c r="C168" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D168" s="25" t="n">
@@ -19734,7 +19734,7 @@
       <x:c r="B169" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C169" s="21" t="n">
+      <x:c r="C169" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D169" s="25" t="n">
@@ -19751,7 +19751,7 @@
       <x:c r="B170" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C170" s="21" t="n">
+      <x:c r="C170" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D170" s="25" t="n">
@@ -19768,7 +19768,7 @@
       <x:c r="B171" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C171" s="21" t="n">
+      <x:c r="C171" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D171" s="20"/>
@@ -19781,7 +19781,7 @@
       <x:c r="B172" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C172" s="21" t="n">
+      <x:c r="C172" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D172" s="25" t="n">
@@ -19798,7 +19798,7 @@
       <x:c r="B173" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C173" s="21" t="n">
+      <x:c r="C173" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D173" s="25" t="n">
@@ -19815,7 +19815,7 @@
       <x:c r="B174" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C174" s="21" t="n">
+      <x:c r="C174" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D174" s="25" t="n">
@@ -19832,7 +19832,7 @@
       <x:c r="B175" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C175" s="21" t="n">
+      <x:c r="C175" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D175" s="25" t="n">
@@ -19849,7 +19849,7 @@
       <x:c r="B176" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C176" s="21" t="n">
+      <x:c r="C176" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D176" s="25" t="n">
@@ -19866,7 +19866,7 @@
       <x:c r="B177" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C177" s="21" t="n">
+      <x:c r="C177" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D177" s="20"/>
@@ -19879,7 +19879,7 @@
       <x:c r="B178" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C178" s="21" t="n">
+      <x:c r="C178" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D178" s="25" t="n">
@@ -19896,7 +19896,7 @@
       <x:c r="B179" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C179" s="21" t="n">
+      <x:c r="C179" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D179" s="25" t="n">
@@ -19913,7 +19913,7 @@
       <x:c r="B180" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C180" s="21" t="n">
+      <x:c r="C180" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D180" s="25" t="n">
@@ -19930,7 +19930,7 @@
       <x:c r="B181" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C181" s="21" t="n">
+      <x:c r="C181" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D181" s="25" t="n">
@@ -19947,7 +19947,7 @@
       <x:c r="B182" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C182" s="21" t="n">
+      <x:c r="C182" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D182" s="25" t="n">
@@ -19964,7 +19964,7 @@
       <x:c r="B183" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C183" s="21" t="n">
+      <x:c r="C183" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D183" s="25" t="n">
@@ -19981,7 +19981,7 @@
       <x:c r="B184" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C184" s="21" t="n">
+      <x:c r="C184" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D184" s="25" t="n">
@@ -19998,7 +19998,7 @@
       <x:c r="B185" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C185" s="21" t="n">
+      <x:c r="C185" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D185" s="25" t="n">
@@ -20015,7 +20015,7 @@
       <x:c r="B186" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C186" s="21" t="n">
+      <x:c r="C186" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D186" s="25" t="n">
@@ -20032,7 +20032,7 @@
       <x:c r="B187" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C187" s="21" t="n">
+      <x:c r="C187" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D187" s="25" t="n">
@@ -20049,7 +20049,7 @@
       <x:c r="B188" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C188" s="21" t="n">
+      <x:c r="C188" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D188" s="25" t="n">
@@ -20066,7 +20066,7 @@
       <x:c r="B189" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C189" s="21" t="n">
+      <x:c r="C189" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D189" s="25" t="n">
@@ -20083,7 +20083,7 @@
       <x:c r="B190" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C190" s="21" t="n">
+      <x:c r="C190" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D190" s="25" t="n">
@@ -20100,7 +20100,7 @@
       <x:c r="B191" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C191" s="21" t="n">
+      <x:c r="C191" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D191" s="25" t="n">
@@ -20117,7 +20117,7 @@
       <x:c r="B192" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C192" s="21" t="n">
+      <x:c r="C192" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D192" s="25" t="n">
@@ -20134,7 +20134,7 @@
       <x:c r="B193" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C193" s="21" t="n">
+      <x:c r="C193" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D193" s="25" t="n">
@@ -20151,7 +20151,7 @@
       <x:c r="B194" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C194" s="21" t="n">
+      <x:c r="C194" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D194" s="25" t="n">
@@ -20168,7 +20168,7 @@
       <x:c r="B195" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C195" s="21" t="n">
+      <x:c r="C195" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D195" s="25" t="n">
@@ -20185,7 +20185,7 @@
       <x:c r="B196" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C196" s="21" t="n">
+      <x:c r="C196" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D196" s="20"/>
@@ -20198,7 +20198,7 @@
       <x:c r="B197" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C197" s="21" t="n">
+      <x:c r="C197" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D197" s="25" t="n">
@@ -20215,7 +20215,7 @@
       <x:c r="B198" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C198" s="21" t="n">
+      <x:c r="C198" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D198" s="25" t="n">
@@ -20232,7 +20232,7 @@
       <x:c r="B199" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C199" s="21" t="n">
+      <x:c r="C199" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D199" s="25" t="n">
@@ -20249,7 +20249,7 @@
       <x:c r="B200" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C200" s="21" t="n">
+      <x:c r="C200" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D200" s="25" t="n">
@@ -20266,7 +20266,7 @@
       <x:c r="B201" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C201" s="21" t="n">
+      <x:c r="C201" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D201" s="25" t="n">
@@ -20283,7 +20283,7 @@
       <x:c r="B202" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C202" s="21" t="n">
+      <x:c r="C202" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D202" s="20"/>
@@ -20296,7 +20296,7 @@
       <x:c r="B203" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C203" s="21" t="n">
+      <x:c r="C203" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D203" s="20"/>
@@ -20309,7 +20309,7 @@
       <x:c r="B204" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C204" s="21" t="n">
+      <x:c r="C204" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D204" s="25" t="n">
@@ -20326,7 +20326,7 @@
       <x:c r="B205" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C205" s="21" t="n">
+      <x:c r="C205" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D205" s="25" t="n">
@@ -20343,7 +20343,7 @@
       <x:c r="B206" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C206" s="21" t="n">
+      <x:c r="C206" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D206" s="25" t="n">
@@ -20360,7 +20360,7 @@
       <x:c r="B207" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C207" s="21" t="n">
+      <x:c r="C207" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D207" s="25" t="n">
@@ -20377,7 +20377,7 @@
       <x:c r="B208" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C208" s="21" t="n">
+      <x:c r="C208" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D208" s="25" t="n">
@@ -20394,7 +20394,7 @@
       <x:c r="B209" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C209" s="21" t="n">
+      <x:c r="C209" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D209" s="25" t="n">
@@ -20411,7 +20411,7 @@
       <x:c r="B210" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C210" s="21" t="n">
+      <x:c r="C210" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D210" s="25" t="n">
@@ -20428,7 +20428,7 @@
       <x:c r="B211" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C211" s="21" t="n">
+      <x:c r="C211" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D211" s="25" t="n">
@@ -20445,7 +20445,7 @@
       <x:c r="B212" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C212" s="21" t="n">
+      <x:c r="C212" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D212" s="25" t="n">
@@ -20462,7 +20462,7 @@
       <x:c r="B213" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C213" s="21" t="n">
+      <x:c r="C213" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D213" s="25" t="n">
@@ -20479,7 +20479,7 @@
       <x:c r="B214" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C214" s="21" t="n">
+      <x:c r="C214" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D214" s="25" t="n">
@@ -20496,7 +20496,7 @@
       <x:c r="B215" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C215" s="21" t="n">
+      <x:c r="C215" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D215" s="25" t="n">
@@ -20513,7 +20513,7 @@
       <x:c r="B216" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C216" s="21" t="n">
+      <x:c r="C216" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D216" s="25" t="n">
@@ -20530,7 +20530,7 @@
       <x:c r="B217" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C217" s="21" t="n">
+      <x:c r="C217" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D217" s="25" t="n">
@@ -20547,7 +20547,7 @@
       <x:c r="B218" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C218" s="21" t="n">
+      <x:c r="C218" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D218" s="25" t="n">
@@ -20564,7 +20564,7 @@
       <x:c r="B219" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C219" s="21" t="n">
+      <x:c r="C219" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D219" s="25" t="n">
@@ -20581,7 +20581,7 @@
       <x:c r="B220" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C220" s="21" t="n">
+      <x:c r="C220" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D220" s="25" t="n">
@@ -20598,7 +20598,7 @@
       <x:c r="B221" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C221" s="21" t="n">
+      <x:c r="C221" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D221" s="25" t="n">
@@ -20615,7 +20615,7 @@
       <x:c r="B222" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C222" s="21" t="n">
+      <x:c r="C222" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D222" s="20"/>
@@ -20628,7 +20628,7 @@
       <x:c r="B223" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C223" s="21" t="n">
+      <x:c r="C223" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D223" s="20"/>
@@ -20641,7 +20641,7 @@
       <x:c r="B224" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C224" s="21" t="n">
+      <x:c r="C224" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D224" s="25" t="n">
@@ -20658,7 +20658,7 @@
       <x:c r="B225" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C225" s="21" t="n">
+      <x:c r="C225" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D225" s="25" t="n">
@@ -20675,7 +20675,7 @@
       <x:c r="B226" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C226" s="21" t="n">
+      <x:c r="C226" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D226" s="25" t="n">
@@ -20692,7 +20692,7 @@
       <x:c r="B227" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C227" s="21" t="n">
+      <x:c r="C227" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D227" s="25" t="n">
@@ -20709,7 +20709,7 @@
       <x:c r="B228" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C228" s="21" t="n">
+      <x:c r="C228" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D228" s="25" t="n">
@@ -20726,7 +20726,7 @@
       <x:c r="B229" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C229" s="21" t="n">
+      <x:c r="C229" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D229" s="20"/>
@@ -20739,7 +20739,7 @@
       <x:c r="B230" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C230" s="21" t="n">
+      <x:c r="C230" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D230" s="20"/>
@@ -20752,7 +20752,7 @@
       <x:c r="B231" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C231" s="21" t="n">
+      <x:c r="C231" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D231" s="25" t="n">
@@ -20769,7 +20769,7 @@
       <x:c r="B232" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C232" s="21" t="n">
+      <x:c r="C232" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D232" s="20"/>
@@ -20782,7 +20782,7 @@
       <x:c r="B233" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C233" s="21" t="n">
+      <x:c r="C233" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D233" s="20"/>
@@ -20795,7 +20795,7 @@
       <x:c r="B234" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C234" s="21" t="n">
+      <x:c r="C234" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D234" s="20"/>
@@ -20808,7 +20808,7 @@
       <x:c r="B235" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C235" s="21" t="n">
+      <x:c r="C235" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D235" s="20"/>
@@ -20821,7 +20821,7 @@
       <x:c r="B236" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C236" s="21" t="n">
+      <x:c r="C236" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D236" s="20"/>
@@ -20834,7 +20834,7 @@
       <x:c r="B237" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C237" s="21" t="n">
+      <x:c r="C237" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D237" s="25" t="n">
@@ -20851,7 +20851,7 @@
       <x:c r="B238" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C238" s="21" t="n">
+      <x:c r="C238" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D238" s="20"/>
@@ -20864,7 +20864,7 @@
       <x:c r="B239" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C239" s="21" t="n">
+      <x:c r="C239" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D239" s="20"/>
@@ -20877,7 +20877,7 @@
       <x:c r="B240" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C240" s="21" t="n">
+      <x:c r="C240" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D240" s="20"/>
@@ -20890,7 +20890,7 @@
       <x:c r="B241" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C241" s="21" t="n">
+      <x:c r="C241" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D241" s="25" t="n">
@@ -20907,7 +20907,7 @@
       <x:c r="B242" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C242" s="21" t="n">
+      <x:c r="C242" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D242" s="20"/>
@@ -20920,7 +20920,7 @@
       <x:c r="B243" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C243" s="21" t="n">
+      <x:c r="C243" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D243" s="20"/>
@@ -20933,7 +20933,7 @@
       <x:c r="B244" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C244" s="21" t="n">
+      <x:c r="C244" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D244" s="20"/>
@@ -20946,7 +20946,7 @@
       <x:c r="B245" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C245" s="21" t="n">
+      <x:c r="C245" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D245" s="20"/>
@@ -20959,7 +20959,7 @@
       <x:c r="B246" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C246" s="21" t="n">
+      <x:c r="C246" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D246" s="20"/>
@@ -20972,7 +20972,7 @@
       <x:c r="B247" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C247" s="21" t="n">
+      <x:c r="C247" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D247" s="20"/>
@@ -20985,7 +20985,7 @@
       <x:c r="B248" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C248" s="21" t="n">
+      <x:c r="C248" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D248" s="25" t="n">
@@ -21002,7 +21002,7 @@
       <x:c r="B249" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C249" s="21" t="n">
+      <x:c r="C249" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D249" s="20"/>
@@ -21015,7 +21015,7 @@
       <x:c r="B250" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C250" s="21" t="n">
+      <x:c r="C250" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D250" s="20"/>
@@ -21028,7 +21028,7 @@
       <x:c r="B251" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C251" s="21" t="n">
+      <x:c r="C251" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D251" s="20"/>
@@ -21041,7 +21041,7 @@
       <x:c r="B252" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C252" s="21" t="n">
+      <x:c r="C252" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D252" s="20"/>
@@ -21054,7 +21054,7 @@
       <x:c r="B253" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C253" s="21" t="n">
+      <x:c r="C253" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D253" s="20"/>
@@ -21067,7 +21067,7 @@
       <x:c r="B254" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C254" s="21" t="n">
+      <x:c r="C254" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D254" s="20"/>
@@ -21080,7 +21080,7 @@
       <x:c r="B255" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C255" s="21" t="n">
+      <x:c r="C255" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D255" s="20"/>
@@ -21093,7 +21093,7 @@
       <x:c r="B256" s="17" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C256" s="21" t="n">
+      <x:c r="C256" s="17" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D256" s="20"/>
@@ -21106,7 +21106,7 @@
       <x:c r="B257" s="17" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C257" s="21" t="n">
+      <x:c r="C257" s="17" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D257" s="20"/>
@@ -21119,7 +21119,7 @@
       <x:c r="B258" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C258" s="21" t="n">
+      <x:c r="C258" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D258" s="25" t="n">
@@ -21136,7 +21136,7 @@
       <x:c r="B259" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C259" s="21" t="n">
+      <x:c r="C259" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D259" s="20"/>
@@ -21149,7 +21149,7 @@
       <x:c r="B260" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C260" s="21" t="n">
+      <x:c r="C260" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D260" s="20"/>
@@ -21162,7 +21162,7 @@
       <x:c r="B261" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C261" s="21" t="n">
+      <x:c r="C261" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D261" s="20"/>
@@ -21175,7 +21175,7 @@
       <x:c r="B262" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C262" s="21" t="n">
+      <x:c r="C262" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D262" s="20"/>
@@ -21188,7 +21188,7 @@
       <x:c r="B263" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C263" s="21" t="n">
+      <x:c r="C263" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D263" s="20"/>
@@ -21201,7 +21201,7 @@
       <x:c r="B264" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C264" s="21" t="n">
+      <x:c r="C264" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D264" s="20"/>
@@ -21214,7 +21214,7 @@
       <x:c r="B265" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C265" s="21" t="n">
+      <x:c r="C265" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D265" s="20"/>
@@ -21227,7 +21227,7 @@
       <x:c r="B266" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C266" s="21" t="n">
+      <x:c r="C266" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D266" s="25" t="n">
@@ -21244,7 +21244,7 @@
       <x:c r="B267" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C267" s="21" t="n">
+      <x:c r="C267" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D267" s="20"/>
@@ -21257,7 +21257,7 @@
       <x:c r="B268" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C268" s="21" t="n">
+      <x:c r="C268" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D268" s="20"/>
@@ -21270,7 +21270,7 @@
       <x:c r="B269" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C269" s="21" t="n">
+      <x:c r="C269" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D269" s="20"/>
@@ -21283,7 +21283,7 @@
       <x:c r="B270" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C270" s="21" t="n">
+      <x:c r="C270" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D270" s="20"/>
@@ -21296,7 +21296,7 @@
       <x:c r="B271" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C271" s="21" t="n">
+      <x:c r="C271" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D271" s="20"/>
@@ -21309,7 +21309,7 @@
       <x:c r="B272" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C272" s="21" t="n">
+      <x:c r="C272" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D272" s="20"/>
@@ -21322,7 +21322,7 @@
       <x:c r="B273" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C273" s="21" t="n">
+      <x:c r="C273" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D273" s="20"/>
@@ -21335,7 +21335,7 @@
       <x:c r="B274" s="17" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C274" s="21" t="n">
+      <x:c r="C274" s="17" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D274" s="20"/>
@@ -21348,7 +21348,7 @@
       <x:c r="B275" s="17" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C275" s="21" t="n">
+      <x:c r="C275" s="17" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D275" s="20"/>
@@ -21361,7 +21361,7 @@
       <x:c r="B276" s="17" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C276" s="21" t="n">
+      <x:c r="C276" s="17" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D276" s="20"/>
@@ -21374,7 +21374,7 @@
       <x:c r="B277" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C277" s="21" t="n">
+      <x:c r="C277" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D277" s="25" t="n">
@@ -21391,7 +21391,7 @@
       <x:c r="B278" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C278" s="21" t="n">
+      <x:c r="C278" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D278" s="20"/>
@@ -21404,7 +21404,7 @@
       <x:c r="B279" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C279" s="21" t="n">
+      <x:c r="C279" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D279" s="20"/>
@@ -21417,7 +21417,7 @@
       <x:c r="B280" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C280" s="21" t="n">
+      <x:c r="C280" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D280" s="20"/>
@@ -21430,7 +21430,7 @@
       <x:c r="B281" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C281" s="21" t="n">
+      <x:c r="C281" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D281" s="20"/>
@@ -21443,7 +21443,7 @@
       <x:c r="B282" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C282" s="21" t="n">
+      <x:c r="C282" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D282" s="25" t="n">
@@ -21460,7 +21460,7 @@
       <x:c r="B283" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C283" s="21" t="n">
+      <x:c r="C283" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D283" s="20"/>
@@ -21473,7 +21473,7 @@
       <x:c r="B284" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C284" s="21" t="n">
+      <x:c r="C284" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D284" s="20"/>
@@ -21486,7 +21486,7 @@
       <x:c r="B285" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C285" s="21" t="n">
+      <x:c r="C285" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D285" s="20"/>
@@ -21499,7 +21499,7 @@
       <x:c r="B286" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C286" s="21" t="n">
+      <x:c r="C286" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D286" s="20"/>
@@ -21512,7 +21512,7 @@
       <x:c r="B287" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C287" s="21" t="n">
+      <x:c r="C287" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D287" s="20"/>
@@ -21525,7 +21525,7 @@
       <x:c r="B288" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C288" s="21" t="n">
+      <x:c r="C288" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D288" s="20"/>
@@ -21568,34 +21568,34 @@
         <x:v>chance</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="138" customHeight="1">
+    <x:row r="2" ht="194" customHeight="1">
       <x:c r="A2" s="10" t="str">
         <x:v>无早段主线实例的既有奖励参考ID
 单位：稳定ID
-约束：仅既有25参考；锁定；不复制有主线来源的预算</x:v>
+约束：仅既有25参考；锁定；不复制有主线来源的预算；固定结构身份列，必须与基线等值，不能只改物理行冒充结构变化</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>参考成员预算块索引
 单位：0起索引
-约束：每参考0..count-1；原95块结构锁定</x:v>
+约束：每参考0..count-1；原95块结构锁定；固定结构身份列，必须与基线等值，不能只改物理行冒充结构变化</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
         <x:v>块内掉落数组顺序
 单位：0起序号
-约束：现有每块一项，order0锁定；不新增条目</x:v>
+约束：现有每块一项，order0锁定；不新增条目；固定结构身份列，必须与基线等值，不能只改物理行冒充结构变化</x:v>
       </x:c>
       <x:c r="D2" s="10" t="str">
-        <x:v>回退掉落资源引用
+        <x:v>既有普通资源ID，当前1为铁；不是无人机专属材料ID。变更须确认资源注册表及预算类型，禁止新增未知资源。
 单位：正式res资源ID
 约束：必须存在于本次正式主线投影resources；不复制资源本身数值</x:v>
       </x:c>
       <x:c r="E2" s="10" t="str">
-        <x:v>仅来源无匹配且资源参考关≤5时的回退掉落数量
+        <x:v>资源参考关≤5且当前主线来源无匹配时的回退单块基础数量。默认8/20，乘资源倍率后发放；调大该块更多，不是专属材料奖励。
 单位：资源份/预算块
 约束：非负有限且&lt;9e15；不影响15已有主线早段模板及40晚段预算</x:v>
       </x:c>
       <x:c r="F2" s="10" t="str">
-        <x:v>该回退掉落发生概率
+        <x:v>该回退块掉落概率0..1，默认1必掉；调大更常出，不改掉落数量。
 单位：概率，1=100%
 约束：有限，0..1</x:v>
       </x:c>

--- a/space-battleship/config_excel/hyperspace_enemies.xlsx
+++ b/space-battleship/config_excel/hyperspace_enemies.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="敌人" sheetId="1" r:id="R6789623c6d9b4363"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器安装" sheetId="2" r:id="Rd0f5fa439d81496a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="编队" sheetId="3" r:id="Re49698843dc3428b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="编队槽位" sheetId="4" r:id="Re7c068b31e104bf0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="路线编排" sheetId="5" r:id="R19390a07dc404aae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励参考" sheetId="6" r:id="R37548412ee21428e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成员分配" sheetId="7" r:id="R3e63c358bc494d43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="早段回退预算" sheetId="8" r:id="Rfe63e82ef4b841a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="敌人" sheetId="1" r:id="R3cfefb505a68423d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="武器安装" sheetId="2" r:id="R811a079a02c5434b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="编队" sheetId="3" r:id="R18de66c0da6943b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="编队槽位" sheetId="4" r:id="Rf45cd07682ee4359"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="路线编排" sheetId="5" r:id="R201a0dc66e3b40c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励参考" sheetId="6" r:id="Rbeb92013217a4026"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成员分配" sheetId="7" r:id="Rd8c15cf4aeda412f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="早段回退预算" sheetId="8" r:id="R22fa6873aeef4bb7"/>
   </x:sheets>
 </x:workbook>
 </file>
